--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  25.08.2025 a 31.08.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  25.08.2025 a 31.08.2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29212"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29225"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1272C625-E869-40E1-9932-09F51C146838}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EF701F6-1797-4B59-9E3F-41697B028C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="25.08" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="120">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -289,6 +289,132 @@
   </si>
   <si>
     <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: HODOMETRO</t>
+  </si>
+  <si>
+    <t>MAURICIO GOMES DE LEMOS FILHO -CPF 77615530172</t>
+  </si>
+  <si>
+    <t>NUP Cancelamento 25.08.2025</t>
+  </si>
+  <si>
+    <t>MARIO SERGIO ANDRADE CPF- 41961480859</t>
+  </si>
+  <si>
+    <t>Chassi irregular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FABIO CEZAR MARCIANO                         </t>
+  </si>
+  <si>
+    <t>Falta de vistoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SORAYA DE OLIVEIRA LIMA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULO SERGIO PEREIRA DINI                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOANA DARC BARROZO CARNEIRO                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRUNO DE OLIVEIRA LUJAN                      </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: CHASSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISAAC BATISTA DE CARVALHO NETO               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOAQUIM MANOEL CARNEIRO                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RHONIERE ALVES ARAUJO                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCOS JOSE DA SILVA                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRISTIANE ARINOS CHAVES DE SOUZA             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GISELE APARECIDA VASQUES FERREIRA BERETTA    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELAINE PAULA DA SILVA LEITE                  </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: Traseira e lateral do motorista, Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOMAS BARBIERI                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MILTON BARBOSA PEREIRA                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">REGINALDO RODRIGUES MARQUES                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">E MORAES E MORAES LTDA EPP                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MILTON JOSE SILVEIRA                         </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: PAINEL COM VEICULO LIGADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YARA FILGUEIRAS BARBOSA ALMEIDA              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEANDRO LUCIO FERREIRA DO NASCIMENTO         </t>
+  </si>
+  <si>
+    <t>F
+avor enviar cópia completa da apólice anterior 2024/2025 (atual) a
+través desse e-mail. (Não será aceito a CI, uma vez em que a CBE n
+ão retorna os dados)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HELENO ALVES RIBEIRO NETO                    </t>
+  </si>
+  <si>
+    <t>PRAZO EXPIRADO. FOTO INCORRETA: CHASSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEVERINO ALBERTO DOS SANTOS FILHO            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FABIANA DA ROCHA PEGUIM                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADNEIA SOUZA DA SILVA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">54 449 481 MARCIA CAMPOS MACHADO ME          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMARILDO DA SILVA MACENA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALEXANDRE DE SOUZA                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">THAIS ELLEN CAXIAS FELIPE                    </t>
+  </si>
+  <si>
+    <t>VOLPMAQ INDUSTRIA E COMERCIO DE MAQUINAS INDU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEANDRO FREIRE DOS SANTOS                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">R C DE SOUSA RCS EPP                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERMISON BISPO DOS SANTOS                     </t>
   </si>
 </sst>
 </file>
@@ -347,7 +473,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -509,12 +635,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -628,7 +774,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -638,11 +783,21 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1059,13 +1214,13 @@
       <c r="C3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="51">
+      <c r="D3" s="25">
         <v>133951577</v>
       </c>
       <c r="E3" s="18">
         <v>3450054839</v>
       </c>
-      <c r="F3" s="47" t="s">
+      <c r="F3" s="12" t="s">
         <v>15</v>
       </c>
       <c r="G3" s="20" t="s">
@@ -1088,19 +1243,19 @@
       <c r="C4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="51">
+      <c r="D4" s="25">
         <v>133968006</v>
       </c>
       <c r="E4" s="18">
         <v>3450056038</v>
       </c>
-      <c r="F4" s="47" t="s">
+      <c r="F4" s="12" t="s">
         <v>18</v>
       </c>
       <c r="G4" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="52" t="s">
+      <c r="H4" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I4" s="27">
@@ -1117,19 +1272,19 @@
       <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="51">
+      <c r="D5" s="25">
         <v>133967991</v>
       </c>
       <c r="E5" s="18">
         <v>3450056027</v>
       </c>
-      <c r="F5" s="47" t="s">
+      <c r="F5" s="12" t="s">
         <v>21</v>
       </c>
       <c r="G5" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="52" t="s">
+      <c r="H5" s="9" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="27">
@@ -1146,13 +1301,13 @@
       <c r="C6" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="51">
+      <c r="D6" s="25">
         <v>133951481</v>
       </c>
       <c r="E6" s="18">
         <v>3450054828</v>
       </c>
-      <c r="F6" s="47" t="s">
+      <c r="F6" s="12" t="s">
         <v>23</v>
       </c>
       <c r="G6" s="20" t="s">
@@ -1175,13 +1330,13 @@
       <c r="C7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="51">
+      <c r="D7" s="25">
         <v>133967394</v>
       </c>
       <c r="E7" s="18">
         <v>3450055972</v>
       </c>
-      <c r="F7" s="47" t="s">
+      <c r="F7" s="12" t="s">
         <v>24</v>
       </c>
       <c r="G7" s="26" t="s">
@@ -1204,13 +1359,13 @@
       <c r="C8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="51">
+      <c r="D8" s="25">
         <v>133949785</v>
       </c>
       <c r="E8" s="18">
         <v>3450054751</v>
       </c>
-      <c r="F8" s="47" t="s">
+      <c r="F8" s="12" t="s">
         <v>25</v>
       </c>
       <c r="G8" s="26" t="s">
@@ -1233,19 +1388,19 @@
       <c r="C9" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="51">
+      <c r="D9" s="25">
         <v>134013450</v>
       </c>
       <c r="E9" s="18">
         <v>3450058403</v>
       </c>
-      <c r="F9" s="47" t="s">
+      <c r="F9" s="12" t="s">
         <v>26</v>
       </c>
       <c r="G9" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="53" t="s">
+      <c r="H9" s="15" t="s">
         <v>27</v>
       </c>
       <c r="I9" s="27">
@@ -1262,19 +1417,19 @@
       <c r="C10" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="51">
+      <c r="D10" s="25">
         <v>134014769</v>
       </c>
       <c r="E10" s="18">
         <v>3450058580</v>
       </c>
-      <c r="F10" s="47" t="s">
+      <c r="F10" s="12" t="s">
         <v>28</v>
       </c>
       <c r="G10" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="53" t="s">
+      <c r="H10" s="15" t="s">
         <v>29</v>
       </c>
       <c r="I10" s="27">
@@ -1291,19 +1446,19 @@
       <c r="C11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="51">
+      <c r="D11" s="25">
         <v>134005066</v>
       </c>
       <c r="E11" s="18">
         <v>3450057875</v>
       </c>
-      <c r="F11" s="47" t="s">
+      <c r="F11" s="12" t="s">
         <v>30</v>
       </c>
       <c r="G11" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="H11" s="52" t="s">
+      <c r="H11" s="9" t="s">
         <v>32</v>
       </c>
       <c r="I11" s="27">
@@ -1320,19 +1475,19 @@
       <c r="C12" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="51">
+      <c r="D12" s="25">
         <v>134002756</v>
       </c>
       <c r="E12" s="18">
         <v>3450057567</v>
       </c>
-      <c r="F12" s="47" t="s">
+      <c r="F12" s="12" t="s">
         <v>33</v>
       </c>
       <c r="G12" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="H12" s="52" t="s">
+      <c r="H12" s="9" t="s">
         <v>35</v>
       </c>
       <c r="I12" s="27">
@@ -1349,19 +1504,19 @@
       <c r="C13" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="51">
+      <c r="D13" s="25">
         <v>134011554</v>
       </c>
       <c r="E13" s="18">
         <v>3450058326</v>
       </c>
-      <c r="F13" s="47" t="s">
+      <c r="F13" s="12" t="s">
         <v>36</v>
       </c>
       <c r="G13" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H13" s="52" t="s">
+      <c r="H13" s="9" t="s">
         <v>37</v>
       </c>
       <c r="I13" s="27">
@@ -1378,19 +1533,19 @@
       <c r="C14" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="51">
+      <c r="D14" s="25">
         <v>134032061</v>
       </c>
       <c r="E14" s="18">
         <v>3450059294</v>
       </c>
-      <c r="F14" s="47" t="s">
+      <c r="F14" s="12" t="s">
         <v>38</v>
       </c>
       <c r="G14" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="H14" s="52" t="s">
+      <c r="H14" s="9" t="s">
         <v>39</v>
       </c>
       <c r="I14" s="27">
@@ -1407,19 +1562,19 @@
       <c r="C15" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="51">
+      <c r="D15" s="25">
         <v>133961746</v>
       </c>
       <c r="E15" s="18">
         <v>3450055543</v>
       </c>
-      <c r="F15" s="47" t="s">
+      <c r="F15" s="12" t="s">
         <v>40</v>
       </c>
       <c r="G15" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="H15" s="52" t="s">
+      <c r="H15" s="9" t="s">
         <v>41</v>
       </c>
       <c r="I15" s="27">
@@ -1436,19 +1591,19 @@
       <c r="C16" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="51">
+      <c r="D16" s="25">
         <v>134051881</v>
       </c>
       <c r="E16" s="18">
         <v>3450060185</v>
       </c>
-      <c r="F16" s="47" t="s">
+      <c r="F16" s="12" t="s">
         <v>42</v>
       </c>
       <c r="G16" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="H16" s="52" t="s">
+      <c r="H16" s="9" t="s">
         <v>44</v>
       </c>
       <c r="I16" s="27">
@@ -1465,19 +1620,19 @@
       <c r="C17" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="51">
+      <c r="D17" s="25">
         <v>134072663</v>
       </c>
       <c r="E17" s="18">
         <v>3450061252</v>
       </c>
-      <c r="F17" s="47" t="s">
+      <c r="F17" s="12" t="s">
         <v>45</v>
       </c>
       <c r="G17" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="H17" s="52" t="s">
+      <c r="H17" s="9" t="s">
         <v>35</v>
       </c>
       <c r="I17" s="27">
@@ -1494,19 +1649,19 @@
       <c r="C18" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="51">
+      <c r="D18" s="25">
         <v>134072098</v>
       </c>
       <c r="E18" s="18">
         <v>3450061208</v>
       </c>
-      <c r="F18" s="47" t="s">
+      <c r="F18" s="12" t="s">
         <v>46</v>
       </c>
       <c r="G18" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="H18" s="52" t="s">
+      <c r="H18" s="9" t="s">
         <v>35</v>
       </c>
       <c r="I18" s="27">
@@ -1523,19 +1678,19 @@
       <c r="C19" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="51">
+      <c r="D19" s="25">
         <v>133997089</v>
       </c>
       <c r="E19" s="18">
         <v>3450057314</v>
       </c>
-      <c r="F19" s="47" t="s">
+      <c r="F19" s="12" t="s">
         <v>47</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H19" s="52" t="s">
+      <c r="H19" s="9" t="s">
         <v>48</v>
       </c>
       <c r="I19" s="27">
@@ -1552,19 +1707,19 @@
       <c r="C20" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D20" s="51">
+      <c r="D20" s="25">
         <v>133888532</v>
       </c>
       <c r="E20" s="18">
         <v>3450051132</v>
       </c>
-      <c r="F20" s="47" t="s">
+      <c r="F20" s="12" t="s">
         <v>49</v>
       </c>
       <c r="G20" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="H20" s="52" t="s">
+      <c r="H20" s="9" t="s">
         <v>50</v>
       </c>
       <c r="I20" s="27">
@@ -1581,13 +1736,13 @@
       <c r="C21" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D21" s="51">
+      <c r="D21" s="25">
         <v>133921740</v>
       </c>
       <c r="E21" s="18">
         <v>3450053321</v>
       </c>
-      <c r="F21" s="47" t="s">
+      <c r="F21" s="12" t="s">
         <v>51</v>
       </c>
       <c r="G21" s="20" t="s">
@@ -1610,19 +1765,19 @@
       <c r="C22" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D22" s="51">
+      <c r="D22" s="25">
         <v>133962059</v>
       </c>
       <c r="E22" s="18">
         <v>3450055565</v>
       </c>
-      <c r="F22" s="47" t="s">
+      <c r="F22" s="12" t="s">
         <v>53</v>
       </c>
       <c r="G22" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H22" s="52" t="s">
+      <c r="H22" s="9" t="s">
         <v>22</v>
       </c>
       <c r="I22" s="27">
@@ -1639,19 +1794,19 @@
       <c r="C23" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="51">
+      <c r="D23" s="25">
         <v>133958216</v>
       </c>
       <c r="E23" s="18">
         <v>3450055356</v>
       </c>
-      <c r="F23" s="47" t="s">
+      <c r="F23" s="12" t="s">
         <v>54</v>
       </c>
       <c r="G23" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H23" s="52" t="s">
+      <c r="H23" s="9" t="s">
         <v>55</v>
       </c>
       <c r="I23" s="27">
@@ -1668,19 +1823,19 @@
       <c r="C24" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="51">
+      <c r="D24" s="25">
         <v>133951650</v>
       </c>
       <c r="E24" s="18">
         <v>3450053277</v>
       </c>
-      <c r="F24" s="47" t="s">
+      <c r="F24" s="12" t="s">
         <v>56</v>
       </c>
       <c r="G24" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H24" s="52" t="s">
+      <c r="H24" s="9" t="s">
         <v>57</v>
       </c>
       <c r="I24" s="27">
@@ -1697,19 +1852,19 @@
       <c r="C25" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="51">
+      <c r="D25" s="25">
         <v>133989708</v>
       </c>
       <c r="E25" s="18">
         <v>3450057040</v>
       </c>
-      <c r="F25" s="47" t="s">
+      <c r="F25" s="12" t="s">
         <v>58</v>
       </c>
       <c r="G25" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H25" s="52" t="s">
+      <c r="H25" s="9" t="s">
         <v>59</v>
       </c>
       <c r="I25" s="27">
@@ -1726,19 +1881,19 @@
       <c r="C26" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="51">
+      <c r="D26" s="25">
         <v>133954717</v>
       </c>
       <c r="E26" s="18">
         <v>3450052771</v>
       </c>
-      <c r="F26" s="47" t="s">
+      <c r="F26" s="12" t="s">
         <v>60</v>
       </c>
       <c r="G26" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H26" s="52" t="s">
+      <c r="H26" s="9" t="s">
         <v>61</v>
       </c>
       <c r="I26" s="27">
@@ -1755,13 +1910,13 @@
       <c r="C27" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="51">
+      <c r="D27" s="25">
         <v>133952751</v>
       </c>
       <c r="E27" s="18">
         <v>3450052970</v>
       </c>
-      <c r="F27" s="47" t="s">
+      <c r="F27" s="12" t="s">
         <v>62</v>
       </c>
       <c r="G27" s="20" t="s">
@@ -1784,13 +1939,13 @@
       <c r="C28" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="51">
+      <c r="D28" s="25">
         <v>133954071</v>
       </c>
       <c r="E28" s="18">
         <v>3450054927</v>
       </c>
-      <c r="F28" s="47" t="s">
+      <c r="F28" s="12" t="s">
         <v>63</v>
       </c>
       <c r="G28" s="20" t="s">
@@ -1813,13 +1968,13 @@
       <c r="C29" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D29" s="51">
+      <c r="D29" s="25">
         <v>133954202</v>
       </c>
       <c r="E29" s="18">
         <v>3450052782</v>
       </c>
-      <c r="F29" s="47" t="s">
+      <c r="F29" s="12" t="s">
         <v>64</v>
       </c>
       <c r="G29" s="20" t="s">
@@ -1842,13 +1997,13 @@
       <c r="C30" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D30" s="51">
+      <c r="D30" s="25">
         <v>133954629</v>
       </c>
       <c r="E30" s="18">
         <v>3450054971</v>
       </c>
-      <c r="F30" s="47" t="s">
+      <c r="F30" s="12" t="s">
         <v>65</v>
       </c>
       <c r="G30" s="20" t="s">
@@ -1871,13 +2026,13 @@
       <c r="C31" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="51">
+      <c r="D31" s="25">
         <v>133956387</v>
       </c>
       <c r="E31" s="18">
         <v>3450055136</v>
       </c>
-      <c r="F31" s="47" t="s">
+      <c r="F31" s="12" t="s">
         <v>66</v>
       </c>
       <c r="G31" s="20" t="s">
@@ -1900,13 +2055,13 @@
       <c r="C32" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D32" s="51">
+      <c r="D32" s="25">
         <v>133959303</v>
       </c>
       <c r="E32" s="18">
         <v>3450055400</v>
       </c>
-      <c r="F32" s="47" t="s">
+      <c r="F32" s="12" t="s">
         <v>67</v>
       </c>
       <c r="G32" s="20" t="s">
@@ -1929,13 +2084,13 @@
       <c r="C33" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D33" s="51">
+      <c r="D33" s="25">
         <v>133960867</v>
       </c>
       <c r="E33" s="18">
         <v>3450055488</v>
       </c>
-      <c r="F33" s="47" t="s">
+      <c r="F33" s="12" t="s">
         <v>68</v>
       </c>
       <c r="G33" s="20" t="s">
@@ -1958,19 +2113,19 @@
       <c r="C34" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D34" s="51">
+      <c r="D34" s="25">
         <v>133980197</v>
       </c>
       <c r="E34" s="18">
         <v>3450055466</v>
       </c>
-      <c r="F34" s="47" t="s">
+      <c r="F34" s="12" t="s">
         <v>69</v>
       </c>
       <c r="G34" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H34" s="52" t="s">
+      <c r="H34" s="9" t="s">
         <v>70</v>
       </c>
       <c r="I34" s="27">
@@ -1987,13 +2142,13 @@
       <c r="C35" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D35" s="51">
+      <c r="D35" s="25">
         <v>133963543</v>
       </c>
       <c r="E35" s="18">
         <v>3450055642</v>
       </c>
-      <c r="F35" s="47" t="s">
+      <c r="F35" s="12" t="s">
         <v>71</v>
       </c>
       <c r="G35" s="20" t="s">
@@ -2016,19 +2171,19 @@
       <c r="C36" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D36" s="51">
+      <c r="D36" s="25">
         <v>133963790</v>
       </c>
       <c r="E36" s="18">
         <v>3450055664</v>
       </c>
-      <c r="F36" s="47" t="s">
+      <c r="F36" s="12" t="s">
         <v>72</v>
       </c>
       <c r="G36" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="H36" s="52" t="s">
+      <c r="H36" s="9" t="s">
         <v>73</v>
       </c>
       <c r="I36" s="27">
@@ -2045,19 +2200,19 @@
       <c r="C37" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D37" s="51">
+      <c r="D37" s="25">
         <v>133975706</v>
       </c>
       <c r="E37" s="18">
         <v>3450056214</v>
       </c>
-      <c r="F37" s="47" t="s">
+      <c r="F37" s="12" t="s">
         <v>74</v>
       </c>
       <c r="G37" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H37" s="52" t="s">
+      <c r="H37" s="9" t="s">
         <v>75</v>
       </c>
       <c r="I37" s="27">
@@ -2074,13 +2229,13 @@
       <c r="C38" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D38" s="51">
+      <c r="D38" s="25">
         <v>133964091</v>
       </c>
       <c r="E38" s="18">
         <v>3450055730</v>
       </c>
-      <c r="F38" s="47" t="s">
+      <c r="F38" s="12" t="s">
         <v>76</v>
       </c>
       <c r="G38" s="24" t="s">
@@ -2103,19 +2258,19 @@
       <c r="C39" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D39" s="51">
+      <c r="D39" s="25">
         <v>134012322</v>
       </c>
       <c r="E39" s="18">
         <v>3450058260</v>
       </c>
-      <c r="F39" s="47" t="s">
+      <c r="F39" s="12" t="s">
         <v>77</v>
       </c>
       <c r="G39" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="H39" s="52" t="s">
+      <c r="H39" s="9" t="s">
         <v>78</v>
       </c>
       <c r="I39" s="27">
@@ -2126,9 +2281,9 @@
       <c r="A40" s="6"/>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
-      <c r="D40" s="48"/>
-      <c r="E40" s="49"/>
-      <c r="F40" s="50"/>
+      <c r="D40" s="47"/>
+      <c r="E40" s="48"/>
+      <c r="F40" s="49"/>
       <c r="G40" s="20"/>
       <c r="H40" s="9"/>
       <c r="I40" s="27"/>
@@ -2322,9 +2477,9 @@
     <col min="3" max="3" width="21.5703125" customWidth="1"/>
     <col min="4" max="4" width="27.7109375" style="17" customWidth="1"/>
     <col min="5" max="5" width="18.5703125" customWidth="1"/>
-    <col min="6" max="6" width="31.5703125" customWidth="1"/>
+    <col min="6" max="6" width="38.5703125" customWidth="1"/>
     <col min="7" max="7" width="19.7109375" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="8" max="8" width="28.140625" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" style="16" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2361,404 +2516,962 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="12"/>
+      <c r="B2" s="7">
+        <v>45877</v>
+      </c>
+      <c r="C2" s="28">
+        <v>45895</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="18">
+        <v>3450049537</v>
+      </c>
+      <c r="F2" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="I2" s="27"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="9"/>
+      <c r="B3" s="7">
+        <v>45891</v>
+      </c>
+      <c r="C3" s="28">
+        <v>45895</v>
+      </c>
+      <c r="D3" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="18">
+        <v>3450060779</v>
+      </c>
+      <c r="F3" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>82</v>
+      </c>
       <c r="I3" s="27"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="27"/>
+      <c r="B4" s="7">
+        <v>45883</v>
+      </c>
+      <c r="C4" s="28">
+        <v>45895</v>
+      </c>
+      <c r="D4" s="54">
+        <v>133978332</v>
+      </c>
+      <c r="E4" s="51">
+        <v>3450054113</v>
+      </c>
+      <c r="F4" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I4" s="27">
+        <v>45883</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="27"/>
+      <c r="B5" s="7">
+        <v>45884</v>
+      </c>
+      <c r="C5" s="28">
+        <v>45895</v>
+      </c>
+      <c r="D5" s="54">
+        <v>133981283</v>
+      </c>
+      <c r="E5" s="51">
+        <v>3450055202</v>
+      </c>
+      <c r="F5" s="50" t="s">
+        <v>85</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I5" s="27">
+        <v>45884</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="27"/>
+      <c r="B6" s="7">
+        <v>45884</v>
+      </c>
+      <c r="C6" s="28">
+        <v>45895</v>
+      </c>
+      <c r="D6" s="54">
+        <v>133985758</v>
+      </c>
+      <c r="E6" s="51">
+        <v>3450056775</v>
+      </c>
+      <c r="F6" s="50" t="s">
+        <v>86</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="I6" s="27">
+        <v>45884</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="27"/>
+      <c r="B7" s="7">
+        <v>45884</v>
+      </c>
+      <c r="C7" s="28">
+        <v>45895</v>
+      </c>
+      <c r="D7" s="54">
+        <v>133980027</v>
+      </c>
+      <c r="E7" s="51">
+        <v>3450055884</v>
+      </c>
+      <c r="F7" s="50" t="s">
+        <v>87</v>
+      </c>
+      <c r="G7" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="I7" s="27">
+        <v>45884</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="27"/>
+      <c r="B8" s="7">
+        <v>45889</v>
+      </c>
+      <c r="C8" s="28">
+        <v>45895</v>
+      </c>
+      <c r="D8" s="54">
+        <v>134028037</v>
+      </c>
+      <c r="E8" s="51">
+        <v>3450058997</v>
+      </c>
+      <c r="F8" s="50" t="s">
+        <v>88</v>
+      </c>
+      <c r="G8" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="55" t="s">
+        <v>89</v>
+      </c>
+      <c r="I8" s="27">
+        <v>45889</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="27"/>
+      <c r="B9" s="7">
+        <v>45892</v>
+      </c>
+      <c r="C9" s="28">
+        <v>45895</v>
+      </c>
+      <c r="D9" s="54">
+        <v>134062392</v>
+      </c>
+      <c r="E9" s="51">
+        <v>3450060768</v>
+      </c>
+      <c r="F9" s="50" t="s">
+        <v>90</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="I9" s="27">
+        <v>45894</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="27"/>
+      <c r="B10" s="7">
+        <v>45887</v>
+      </c>
+      <c r="C10" s="28">
+        <v>45895</v>
+      </c>
+      <c r="D10" s="54">
+        <v>133976697</v>
+      </c>
+      <c r="E10" s="51">
+        <v>3450056258</v>
+      </c>
+      <c r="F10" s="50" t="s">
+        <v>91</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I10" s="27">
+        <v>45887</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="27"/>
+      <c r="B11" s="7">
+        <v>45891</v>
+      </c>
+      <c r="C11" s="28">
+        <v>45895</v>
+      </c>
+      <c r="D11" s="54">
+        <v>134069140</v>
+      </c>
+      <c r="E11" s="51">
+        <v>3450060988</v>
+      </c>
+      <c r="F11" s="50" t="s">
+        <v>92</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="I11" s="27">
+        <v>45894</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="27"/>
+      <c r="B12" s="7">
+        <v>45905</v>
+      </c>
+      <c r="C12" s="28">
+        <v>45895</v>
+      </c>
+      <c r="D12" s="54">
+        <v>134071914</v>
+      </c>
+      <c r="E12" s="51">
+        <v>3450061186</v>
+      </c>
+      <c r="F12" s="50" t="s">
+        <v>93</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="I12" s="27">
+        <v>45894</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="27"/>
+      <c r="B13" s="7">
+        <v>45889</v>
+      </c>
+      <c r="C13" s="28">
+        <v>45895</v>
+      </c>
+      <c r="D13" s="54">
+        <v>134032849</v>
+      </c>
+      <c r="E13" s="51">
+        <v>3450059349</v>
+      </c>
+      <c r="F13" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="I13" s="27">
+        <v>45894</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="27"/>
+      <c r="B14" s="7">
+        <v>45891</v>
+      </c>
+      <c r="C14" s="28">
+        <v>45895</v>
+      </c>
+      <c r="D14" s="54">
+        <v>134075165</v>
+      </c>
+      <c r="E14" s="51">
+        <v>3450061373</v>
+      </c>
+      <c r="F14" s="50" t="s">
+        <v>95</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="I14" s="27">
+        <v>45894</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="27"/>
+      <c r="B15" s="7">
+        <v>45887</v>
+      </c>
+      <c r="C15" s="28">
+        <v>45895</v>
+      </c>
+      <c r="D15" s="54">
+        <v>133991881</v>
+      </c>
+      <c r="E15" s="51">
+        <v>3450057215</v>
+      </c>
+      <c r="F15" s="50" t="s">
+        <v>96</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" s="56" t="s">
+        <v>97</v>
+      </c>
+      <c r="I15" s="27">
+        <v>45887</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="27"/>
+      <c r="B16" s="7">
+        <v>45891</v>
+      </c>
+      <c r="C16" s="28">
+        <v>45895</v>
+      </c>
+      <c r="D16" s="54">
+        <v>134080037</v>
+      </c>
+      <c r="E16" s="51">
+        <v>3450061648</v>
+      </c>
+      <c r="F16" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H16" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" s="27">
+        <v>45891</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="27"/>
+      <c r="B17" s="7">
+        <v>45891</v>
+      </c>
+      <c r="C17" s="28">
+        <v>45895</v>
+      </c>
+      <c r="D17" s="54">
+        <v>134082173</v>
+      </c>
+      <c r="E17" s="51">
+        <v>3450061802</v>
+      </c>
+      <c r="F17" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H17" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="I17" s="27">
+        <v>45891</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="27"/>
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="7">
+        <v>45889</v>
+      </c>
+      <c r="C18" s="28">
+        <v>45895</v>
+      </c>
+      <c r="D18" s="54">
+        <v>134097930</v>
+      </c>
+      <c r="E18" s="51">
+        <v>3450058854</v>
+      </c>
+      <c r="F18" s="50" t="s">
+        <v>100</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H18" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="I18" s="27">
+        <v>45889</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="27"/>
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>45884</v>
+      </c>
+      <c r="C19" s="28">
+        <v>45895</v>
+      </c>
+      <c r="D19" s="54">
+        <v>133980373</v>
+      </c>
+      <c r="E19" s="51">
+        <v>3450055378</v>
+      </c>
+      <c r="F19" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" s="56" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" s="27">
+        <v>45884</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="27"/>
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>45889</v>
+      </c>
+      <c r="C20" s="28">
+        <v>45895</v>
+      </c>
+      <c r="D20" s="54">
+        <v>134034881</v>
+      </c>
+      <c r="E20" s="51">
+        <v>3450059460</v>
+      </c>
+      <c r="F20" s="50" t="s">
+        <v>102</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" s="56" t="s">
+        <v>103</v>
+      </c>
+      <c r="I20" s="27">
+        <v>45889</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="27"/>
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>45888</v>
+      </c>
+      <c r="C21" s="28">
+        <v>45895</v>
+      </c>
+      <c r="D21" s="54">
+        <v>133997076</v>
+      </c>
+      <c r="E21" s="51">
+        <v>3450057303</v>
+      </c>
+      <c r="F21" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="I21" s="27">
+        <v>45894</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="27"/>
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>45888</v>
+      </c>
+      <c r="C22" s="28">
+        <v>45895</v>
+      </c>
+      <c r="D22" s="54">
+        <v>133922899</v>
+      </c>
+      <c r="E22" s="51">
+        <v>3450053420</v>
+      </c>
+      <c r="F22" s="50" t="s">
+        <v>105</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" s="56" t="s">
+        <v>106</v>
+      </c>
+      <c r="I22" s="27">
+        <v>45884</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="27"/>
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>45887</v>
+      </c>
+      <c r="C23" s="28">
+        <v>45895</v>
+      </c>
+      <c r="D23" s="54">
+        <v>133982224</v>
+      </c>
+      <c r="E23" s="51">
+        <v>3450056588</v>
+      </c>
+      <c r="F23" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23" s="56" t="s">
+        <v>108</v>
+      </c>
+      <c r="I23" s="27">
+        <v>45887</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="27"/>
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>45887</v>
+      </c>
+      <c r="C24" s="28">
+        <v>45895</v>
+      </c>
+      <c r="D24" s="54">
+        <v>133974816</v>
+      </c>
+      <c r="E24" s="51">
+        <v>3450056192</v>
+      </c>
+      <c r="F24" s="50" t="s">
+        <v>109</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I24" s="27">
+        <v>45887</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="27"/>
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>45883</v>
+      </c>
+      <c r="C25" s="28">
+        <v>45895</v>
+      </c>
+      <c r="D25" s="54">
+        <v>133978116</v>
+      </c>
+      <c r="E25" s="51">
+        <v>3450054135</v>
+      </c>
+      <c r="F25" s="50" t="s">
+        <v>110</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="I25" s="27">
+        <v>45883</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="27"/>
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="7">
+        <v>45887</v>
+      </c>
+      <c r="C26" s="28">
+        <v>45895</v>
+      </c>
+      <c r="D26" s="54">
+        <v>133980382</v>
+      </c>
+      <c r="E26" s="51">
+        <v>3450056490</v>
+      </c>
+      <c r="F26" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="I26" s="27">
+        <v>45887</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="27"/>
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="7">
+        <v>45887</v>
+      </c>
+      <c r="C27" s="28">
+        <v>45895</v>
+      </c>
+      <c r="D27" s="54">
+        <v>133981246</v>
+      </c>
+      <c r="E27" s="51">
+        <v>3450056577</v>
+      </c>
+      <c r="F27" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I27" s="27">
+        <v>45887</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="27"/>
+      <c r="A28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="7">
+        <v>45884</v>
+      </c>
+      <c r="C28" s="28">
+        <v>45895</v>
+      </c>
+      <c r="D28" s="54">
+        <v>133981548</v>
+      </c>
+      <c r="E28" s="51">
+        <v>3450054949</v>
+      </c>
+      <c r="F28" s="50" t="s">
+        <v>113</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I28" s="27">
+        <v>45884</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="27"/>
+      <c r="A29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="7">
+        <v>45884</v>
+      </c>
+      <c r="C29" s="28">
+        <v>45895</v>
+      </c>
+      <c r="D29" s="54">
+        <v>133982313</v>
+      </c>
+      <c r="E29" s="51">
+        <v>3450054806</v>
+      </c>
+      <c r="F29" s="50" t="s">
+        <v>114</v>
+      </c>
+      <c r="G29" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I29" s="27">
+        <v>45884</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="6"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="27"/>
+      <c r="A30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="7">
+        <v>45887</v>
+      </c>
+      <c r="C30" s="28">
+        <v>45895</v>
+      </c>
+      <c r="D30" s="54">
+        <v>133987942</v>
+      </c>
+      <c r="E30" s="51">
+        <v>3450056852</v>
+      </c>
+      <c r="F30" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="G30" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I30" s="27">
+        <v>45887</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="27"/>
+      <c r="A31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="7">
+        <v>45887</v>
+      </c>
+      <c r="C31" s="28">
+        <v>45895</v>
+      </c>
+      <c r="D31" s="54">
+        <v>133988895</v>
+      </c>
+      <c r="E31" s="51">
+        <v>3450056973</v>
+      </c>
+      <c r="F31" s="50" t="s">
+        <v>116</v>
+      </c>
+      <c r="G31" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I31" s="27">
+        <v>45887</v>
+      </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="27"/>
+      <c r="A32" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="7">
+        <v>45887</v>
+      </c>
+      <c r="C32" s="28">
+        <v>45895</v>
+      </c>
+      <c r="D32" s="54">
+        <v>133989544</v>
+      </c>
+      <c r="E32" s="51">
+        <v>3450057028</v>
+      </c>
+      <c r="F32" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="G32" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I32" s="27">
+        <v>45887</v>
+      </c>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="6"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="27"/>
+      <c r="A33" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="7">
+        <v>45887</v>
+      </c>
+      <c r="C33" s="28">
+        <v>45895</v>
+      </c>
+      <c r="D33" s="54">
+        <v>133990516</v>
+      </c>
+      <c r="E33" s="51">
+        <v>3450057094</v>
+      </c>
+      <c r="F33" s="50" t="s">
+        <v>118</v>
+      </c>
+      <c r="G33" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I33" s="27">
+        <v>45887</v>
+      </c>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" s="6"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="23"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="27"/>
+      <c r="A34" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="7">
+        <v>45887</v>
+      </c>
+      <c r="C34" s="28">
+        <v>45895</v>
+      </c>
+      <c r="D34" s="54">
+        <v>133990572</v>
+      </c>
+      <c r="E34" s="52">
+        <v>3450057105</v>
+      </c>
+      <c r="F34" s="50" t="s">
+        <v>119</v>
+      </c>
+      <c r="G34" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I34" s="27">
+        <v>45887</v>
+      </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="6"/>
       <c r="B35" s="8"/>
       <c r="C35" s="7"/>
-      <c r="D35" s="8"/>
+      <c r="D35" s="23"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="9"/>
+      <c r="F35" s="15"/>
       <c r="G35" s="6"/>
       <c r="H35" s="9"/>
       <c r="I35" s="27"/>
@@ -2985,12 +3698,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="4">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A33" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A34" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
       <formula1>$J$2</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{5FAA0C61-6912-46B8-8149-B719594B77CB}">
@@ -6116,49 +6829,65 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-494894</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-494894</Url>
-      <Description>QAFFA7D2F2TC-2102087286-494894</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="43" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="abf1b9912853fe4a934dbc2373304754">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d8d96f03b10d24171ef462918d18284e" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -6530,77 +7259,61 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-494894</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-494894</Url>
+      <Description>QAFFA7D2F2TC-2102087286-494894</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098F1F3C-7054-44DA-97C1-1FA0AD811FFC}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  25.08.2025 a 31.08.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  25.08.2025 a 31.08.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EF701F6-1797-4B59-9E3F-41697B028C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A9897DA-E3C6-4F84-A4A8-2F2CF258BD76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="25.08" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="166">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -415,6 +415,146 @@
   </si>
   <si>
     <t xml:space="preserve">ERMISON BISPO DOS SANTOS                     </t>
+  </si>
+  <si>
+    <t>22/08/2025</t>
+  </si>
+  <si>
+    <t>27/08/2025</t>
+  </si>
+  <si>
+    <t>KAUE INACIO FERNANDES  CPF 37003893886</t>
+  </si>
+  <si>
+    <t>NUP cancelamento 26.08.2025</t>
+  </si>
+  <si>
+    <t>19/08/2025</t>
+  </si>
+  <si>
+    <t>ANA PAULA WANDERLEY SILVA CPF 07167541427</t>
+  </si>
+  <si>
+    <t>Apolice ativa de outro corretor</t>
+  </si>
+  <si>
+    <t>LEONARDO SILVA OLIVEIRA CPF 07139699542</t>
+  </si>
+  <si>
+    <t>Chassi Irregular</t>
+  </si>
+  <si>
+    <t>21/08/2025</t>
+  </si>
+  <si>
+    <t>SANDRO REGINALDO CAMARGO RODRIGUES CPF 02241244988</t>
+  </si>
+  <si>
+    <t>Prop ativa de outro corretror</t>
+  </si>
+  <si>
+    <t>EVANDES PEREIRA MIRANDA CPF 61721158391</t>
+  </si>
+  <si>
+    <t>CELSO HENRIQUE TENORIO CPF 22381492879</t>
+  </si>
+  <si>
+    <t>26/08/2025</t>
+  </si>
+  <si>
+    <t>SARA HORACIO DE OLIVEIRA MACIEL CPF 66609674434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MILENE FLORIO BONOTO VIAL                    </t>
+  </si>
+  <si>
+    <t>Duplicidade;</t>
+  </si>
+  <si>
+    <t>Informamos que a proposta em questão se encontra em duplicidade co
+m a apólice 5177202551311321106, para prosseguirmos com a emissão
+se faz necessário realizar o cancelamento da mesma.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUELI DO PRADO MACEDO                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">R O FERREIRA SERVICOS DE PINTURA ME          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SWEET E COCO LTDA ME                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALISON SANTOS DA SILVA                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALINE KEMER TAMADA DA ROCHA MATTOS           </t>
+  </si>
+  <si>
+    <t>CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: TODAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENIVALDO DA SILVA MOURA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCOS JOSE DO AMARAL                        </t>
+  </si>
+  <si>
+    <t>P MENEZES COMERCIO DE ARTIGOS DE PESCA LTDA M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAMELA TEIXEIRA BRASILEIRO                   </t>
+  </si>
+  <si>
+    <t>NUP Cancelamento 26.08.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLAUCIA NUNES VIDAL DOBBIN                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A P O LIMA SILVA SERVICOS LTDA ME            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">THAIS GERDULI DE CAMPOS DAMASCENO            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDILENE GOMES TELLES                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTI PREVI GESTAO E NEGOCIOS LTDA EPP       </t>
+  </si>
+  <si>
+    <t>PRAZO EXPIRADO. Fotos que tiveram repique: Painel com carro ligado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALESSANDRO MARTINS COELHO                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SILVA DISTRIBUIDORA DE CIMENTO LTDA ME       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODILEI FERNEDA RANDO                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SONIA MARIA MACHADO                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GF COMERCIO DE FERRO E ACO EM GERAL LTDA ME  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NICOLODI NICOLODI LTDA ME                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSANGELA APARECIDA CAETANO SANCHES          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUCILEI INACIO MARTINS                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAYANE DESONE SILVA                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRUNO VINICIUS ISAAC COSTA                   </t>
   </si>
 </sst>
 </file>
@@ -660,7 +800,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -783,7 +923,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -791,6 +930,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2528,7 +2677,7 @@
       <c r="E2" s="18">
         <v>3450049537</v>
       </c>
-      <c r="F2" s="55" t="s">
+      <c r="F2" s="12" t="s">
         <v>79</v>
       </c>
       <c r="G2" s="20" t="s">
@@ -2549,7 +2698,7 @@
       <c r="C3" s="28">
         <v>45895</v>
       </c>
-      <c r="D3" s="53" t="s">
+      <c r="D3" s="52" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="18">
@@ -2576,13 +2725,13 @@
       <c r="C4" s="28">
         <v>45895</v>
       </c>
-      <c r="D4" s="54">
+      <c r="D4" s="25">
         <v>133978332</v>
       </c>
-      <c r="E4" s="51">
+      <c r="E4" s="50">
         <v>3450054113</v>
       </c>
-      <c r="F4" s="50" t="s">
+      <c r="F4" s="12" t="s">
         <v>83</v>
       </c>
       <c r="G4" s="20" t="s">
@@ -2605,13 +2754,13 @@
       <c r="C5" s="28">
         <v>45895</v>
       </c>
-      <c r="D5" s="54">
+      <c r="D5" s="25">
         <v>133981283</v>
       </c>
-      <c r="E5" s="51">
+      <c r="E5" s="50">
         <v>3450055202</v>
       </c>
-      <c r="F5" s="50" t="s">
+      <c r="F5" s="12" t="s">
         <v>85</v>
       </c>
       <c r="G5" s="20" t="s">
@@ -2634,13 +2783,13 @@
       <c r="C6" s="28">
         <v>45895</v>
       </c>
-      <c r="D6" s="54">
+      <c r="D6" s="25">
         <v>133985758</v>
       </c>
-      <c r="E6" s="51">
+      <c r="E6" s="50">
         <v>3450056775</v>
       </c>
-      <c r="F6" s="50" t="s">
+      <c r="F6" s="12" t="s">
         <v>86</v>
       </c>
       <c r="G6" s="20" t="s">
@@ -2663,13 +2812,13 @@
       <c r="C7" s="28">
         <v>45895</v>
       </c>
-      <c r="D7" s="54">
+      <c r="D7" s="25">
         <v>133980027</v>
       </c>
-      <c r="E7" s="51">
+      <c r="E7" s="50">
         <v>3450055884</v>
       </c>
-      <c r="F7" s="50" t="s">
+      <c r="F7" s="12" t="s">
         <v>87</v>
       </c>
       <c r="G7" s="26" t="s">
@@ -2692,19 +2841,19 @@
       <c r="C8" s="28">
         <v>45895</v>
       </c>
-      <c r="D8" s="54">
+      <c r="D8" s="25">
         <v>134028037</v>
       </c>
-      <c r="E8" s="51">
+      <c r="E8" s="50">
         <v>3450058997</v>
       </c>
-      <c r="F8" s="50" t="s">
+      <c r="F8" s="12" t="s">
         <v>88</v>
       </c>
       <c r="G8" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="55" t="s">
+      <c r="H8" s="12" t="s">
         <v>89</v>
       </c>
       <c r="I8" s="27">
@@ -2721,13 +2870,13 @@
       <c r="C9" s="28">
         <v>45895</v>
       </c>
-      <c r="D9" s="54">
+      <c r="D9" s="25">
         <v>134062392</v>
       </c>
-      <c r="E9" s="51">
+      <c r="E9" s="50">
         <v>3450060768</v>
       </c>
-      <c r="F9" s="50" t="s">
+      <c r="F9" s="12" t="s">
         <v>90</v>
       </c>
       <c r="G9" s="20" t="s">
@@ -2750,13 +2899,13 @@
       <c r="C10" s="28">
         <v>45895</v>
       </c>
-      <c r="D10" s="54">
+      <c r="D10" s="25">
         <v>133976697</v>
       </c>
-      <c r="E10" s="51">
+      <c r="E10" s="50">
         <v>3450056258</v>
       </c>
-      <c r="F10" s="50" t="s">
+      <c r="F10" s="12" t="s">
         <v>91</v>
       </c>
       <c r="G10" s="20" t="s">
@@ -2779,13 +2928,13 @@
       <c r="C11" s="28">
         <v>45895</v>
       </c>
-      <c r="D11" s="54">
+      <c r="D11" s="25">
         <v>134069140</v>
       </c>
-      <c r="E11" s="51">
+      <c r="E11" s="50">
         <v>3450060988</v>
       </c>
-      <c r="F11" s="50" t="s">
+      <c r="F11" s="12" t="s">
         <v>92</v>
       </c>
       <c r="G11" s="20" t="s">
@@ -2808,13 +2957,13 @@
       <c r="C12" s="28">
         <v>45895</v>
       </c>
-      <c r="D12" s="54">
+      <c r="D12" s="25">
         <v>134071914</v>
       </c>
-      <c r="E12" s="51">
+      <c r="E12" s="50">
         <v>3450061186</v>
       </c>
-      <c r="F12" s="50" t="s">
+      <c r="F12" s="12" t="s">
         <v>93</v>
       </c>
       <c r="G12" s="20" t="s">
@@ -2837,13 +2986,13 @@
       <c r="C13" s="28">
         <v>45895</v>
       </c>
-      <c r="D13" s="54">
+      <c r="D13" s="25">
         <v>134032849</v>
       </c>
-      <c r="E13" s="51">
+      <c r="E13" s="50">
         <v>3450059349</v>
       </c>
-      <c r="F13" s="50" t="s">
+      <c r="F13" s="12" t="s">
         <v>94</v>
       </c>
       <c r="G13" s="20" t="s">
@@ -2866,13 +3015,13 @@
       <c r="C14" s="28">
         <v>45895</v>
       </c>
-      <c r="D14" s="54">
+      <c r="D14" s="25">
         <v>134075165</v>
       </c>
-      <c r="E14" s="51">
+      <c r="E14" s="50">
         <v>3450061373</v>
       </c>
-      <c r="F14" s="50" t="s">
+      <c r="F14" s="12" t="s">
         <v>95</v>
       </c>
       <c r="G14" s="20" t="s">
@@ -2895,19 +3044,19 @@
       <c r="C15" s="28">
         <v>45895</v>
       </c>
-      <c r="D15" s="54">
+      <c r="D15" s="25">
         <v>133991881</v>
       </c>
-      <c r="E15" s="51">
+      <c r="E15" s="50">
         <v>3450057215</v>
       </c>
-      <c r="F15" s="50" t="s">
+      <c r="F15" s="12" t="s">
         <v>96</v>
       </c>
       <c r="G15" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="56" t="s">
+      <c r="H15" s="9" t="s">
         <v>97</v>
       </c>
       <c r="I15" s="27">
@@ -2924,19 +3073,19 @@
       <c r="C16" s="28">
         <v>45895</v>
       </c>
-      <c r="D16" s="54">
+      <c r="D16" s="25">
         <v>134080037</v>
       </c>
-      <c r="E16" s="51">
+      <c r="E16" s="50">
         <v>3450061648</v>
       </c>
-      <c r="F16" s="50" t="s">
+      <c r="F16" s="12" t="s">
         <v>98</v>
       </c>
       <c r="G16" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="H16" s="56" t="s">
+      <c r="H16" s="9" t="s">
         <v>35</v>
       </c>
       <c r="I16" s="27">
@@ -2953,19 +3102,19 @@
       <c r="C17" s="28">
         <v>45895</v>
       </c>
-      <c r="D17" s="54">
+      <c r="D17" s="25">
         <v>134082173</v>
       </c>
-      <c r="E17" s="51">
+      <c r="E17" s="50">
         <v>3450061802</v>
       </c>
-      <c r="F17" s="50" t="s">
+      <c r="F17" s="12" t="s">
         <v>99</v>
       </c>
       <c r="G17" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="H17" s="56" t="s">
+      <c r="H17" s="9" t="s">
         <v>35</v>
       </c>
       <c r="I17" s="27">
@@ -2982,19 +3131,19 @@
       <c r="C18" s="28">
         <v>45895</v>
       </c>
-      <c r="D18" s="54">
+      <c r="D18" s="25">
         <v>134097930</v>
       </c>
-      <c r="E18" s="51">
+      <c r="E18" s="50">
         <v>3450058854</v>
       </c>
-      <c r="F18" s="50" t="s">
+      <c r="F18" s="12" t="s">
         <v>100</v>
       </c>
       <c r="G18" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="H18" s="56" t="s">
+      <c r="H18" s="9" t="s">
         <v>35</v>
       </c>
       <c r="I18" s="27">
@@ -3011,19 +3160,19 @@
       <c r="C19" s="28">
         <v>45895</v>
       </c>
-      <c r="D19" s="54">
+      <c r="D19" s="25">
         <v>133980373</v>
       </c>
-      <c r="E19" s="51">
+      <c r="E19" s="50">
         <v>3450055378</v>
       </c>
-      <c r="F19" s="50" t="s">
+      <c r="F19" s="12" t="s">
         <v>101</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H19" s="56" t="s">
+      <c r="H19" s="9" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="27">
@@ -3040,19 +3189,19 @@
       <c r="C20" s="28">
         <v>45895</v>
       </c>
-      <c r="D20" s="54">
+      <c r="D20" s="25">
         <v>134034881</v>
       </c>
-      <c r="E20" s="51">
+      <c r="E20" s="50">
         <v>3450059460</v>
       </c>
-      <c r="F20" s="50" t="s">
+      <c r="F20" s="12" t="s">
         <v>102</v>
       </c>
       <c r="G20" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H20" s="56" t="s">
+      <c r="H20" s="9" t="s">
         <v>103</v>
       </c>
       <c r="I20" s="27">
@@ -3069,13 +3218,13 @@
       <c r="C21" s="28">
         <v>45895</v>
       </c>
-      <c r="D21" s="54">
+      <c r="D21" s="25">
         <v>133997076</v>
       </c>
-      <c r="E21" s="51">
+      <c r="E21" s="50">
         <v>3450057303</v>
       </c>
-      <c r="F21" s="50" t="s">
+      <c r="F21" s="12" t="s">
         <v>104</v>
       </c>
       <c r="G21" s="20" t="s">
@@ -3098,19 +3247,19 @@
       <c r="C22" s="28">
         <v>45895</v>
       </c>
-      <c r="D22" s="54">
+      <c r="D22" s="25">
         <v>133922899</v>
       </c>
-      <c r="E22" s="51">
+      <c r="E22" s="50">
         <v>3450053420</v>
       </c>
-      <c r="F22" s="50" t="s">
+      <c r="F22" s="12" t="s">
         <v>105</v>
       </c>
       <c r="G22" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="H22" s="56" t="s">
+      <c r="H22" s="9" t="s">
         <v>106</v>
       </c>
       <c r="I22" s="27">
@@ -3127,19 +3276,19 @@
       <c r="C23" s="28">
         <v>45895</v>
       </c>
-      <c r="D23" s="54">
+      <c r="D23" s="25">
         <v>133982224</v>
       </c>
-      <c r="E23" s="51">
+      <c r="E23" s="50">
         <v>3450056588</v>
       </c>
-      <c r="F23" s="50" t="s">
+      <c r="F23" s="12" t="s">
         <v>107</v>
       </c>
       <c r="G23" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H23" s="56" t="s">
+      <c r="H23" s="9" t="s">
         <v>108</v>
       </c>
       <c r="I23" s="27">
@@ -3156,13 +3305,13 @@
       <c r="C24" s="28">
         <v>45895</v>
       </c>
-      <c r="D24" s="54">
+      <c r="D24" s="25">
         <v>133974816</v>
       </c>
-      <c r="E24" s="51">
+      <c r="E24" s="50">
         <v>3450056192</v>
       </c>
-      <c r="F24" s="50" t="s">
+      <c r="F24" s="12" t="s">
         <v>109</v>
       </c>
       <c r="G24" s="20" t="s">
@@ -3185,13 +3334,13 @@
       <c r="C25" s="28">
         <v>45895</v>
       </c>
-      <c r="D25" s="54">
+      <c r="D25" s="25">
         <v>133978116</v>
       </c>
-      <c r="E25" s="51">
+      <c r="E25" s="50">
         <v>3450054135</v>
       </c>
-      <c r="F25" s="50" t="s">
+      <c r="F25" s="12" t="s">
         <v>110</v>
       </c>
       <c r="G25" s="20" t="s">
@@ -3214,13 +3363,13 @@
       <c r="C26" s="28">
         <v>45895</v>
       </c>
-      <c r="D26" s="54">
+      <c r="D26" s="25">
         <v>133980382</v>
       </c>
-      <c r="E26" s="51">
+      <c r="E26" s="50">
         <v>3450056490</v>
       </c>
-      <c r="F26" s="50" t="s">
+      <c r="F26" s="12" t="s">
         <v>111</v>
       </c>
       <c r="G26" s="20" t="s">
@@ -3243,13 +3392,13 @@
       <c r="C27" s="28">
         <v>45895</v>
       </c>
-      <c r="D27" s="54">
+      <c r="D27" s="25">
         <v>133981246</v>
       </c>
-      <c r="E27" s="51">
+      <c r="E27" s="50">
         <v>3450056577</v>
       </c>
-      <c r="F27" s="50" t="s">
+      <c r="F27" s="12" t="s">
         <v>112</v>
       </c>
       <c r="G27" s="20" t="s">
@@ -3272,13 +3421,13 @@
       <c r="C28" s="28">
         <v>45895</v>
       </c>
-      <c r="D28" s="54">
+      <c r="D28" s="25">
         <v>133981548</v>
       </c>
-      <c r="E28" s="51">
+      <c r="E28" s="50">
         <v>3450054949</v>
       </c>
-      <c r="F28" s="50" t="s">
+      <c r="F28" s="12" t="s">
         <v>113</v>
       </c>
       <c r="G28" s="20" t="s">
@@ -3301,13 +3450,13 @@
       <c r="C29" s="28">
         <v>45895</v>
       </c>
-      <c r="D29" s="54">
+      <c r="D29" s="25">
         <v>133982313</v>
       </c>
-      <c r="E29" s="51">
+      <c r="E29" s="50">
         <v>3450054806</v>
       </c>
-      <c r="F29" s="50" t="s">
+      <c r="F29" s="12" t="s">
         <v>114</v>
       </c>
       <c r="G29" s="20" t="s">
@@ -3330,13 +3479,13 @@
       <c r="C30" s="28">
         <v>45895</v>
       </c>
-      <c r="D30" s="54">
+      <c r="D30" s="25">
         <v>133987942</v>
       </c>
-      <c r="E30" s="51">
+      <c r="E30" s="50">
         <v>3450056852</v>
       </c>
-      <c r="F30" s="50" t="s">
+      <c r="F30" s="12" t="s">
         <v>115</v>
       </c>
       <c r="G30" s="20" t="s">
@@ -3359,13 +3508,13 @@
       <c r="C31" s="28">
         <v>45895</v>
       </c>
-      <c r="D31" s="54">
+      <c r="D31" s="25">
         <v>133988895</v>
       </c>
-      <c r="E31" s="51">
+      <c r="E31" s="50">
         <v>3450056973</v>
       </c>
-      <c r="F31" s="50" t="s">
+      <c r="F31" s="12" t="s">
         <v>116</v>
       </c>
       <c r="G31" s="20" t="s">
@@ -3388,13 +3537,13 @@
       <c r="C32" s="28">
         <v>45895</v>
       </c>
-      <c r="D32" s="54">
+      <c r="D32" s="25">
         <v>133989544</v>
       </c>
-      <c r="E32" s="51">
+      <c r="E32" s="50">
         <v>3450057028</v>
       </c>
-      <c r="F32" s="50" t="s">
+      <c r="F32" s="12" t="s">
         <v>117</v>
       </c>
       <c r="G32" s="20" t="s">
@@ -3417,13 +3566,13 @@
       <c r="C33" s="28">
         <v>45895</v>
       </c>
-      <c r="D33" s="54">
+      <c r="D33" s="25">
         <v>133990516</v>
       </c>
-      <c r="E33" s="51">
+      <c r="E33" s="50">
         <v>3450057094</v>
       </c>
-      <c r="F33" s="50" t="s">
+      <c r="F33" s="12" t="s">
         <v>118</v>
       </c>
       <c r="G33" s="20" t="s">
@@ -3446,13 +3595,13 @@
       <c r="C34" s="28">
         <v>45895</v>
       </c>
-      <c r="D34" s="54">
+      <c r="D34" s="25">
         <v>133990572</v>
       </c>
-      <c r="E34" s="52">
+      <c r="E34" s="51">
         <v>3450057105</v>
       </c>
-      <c r="F34" s="50" t="s">
+      <c r="F34" s="12" t="s">
         <v>119</v>
       </c>
       <c r="G34" s="20" t="s">
@@ -3716,14 +3865,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BD26F43-5C8A-4C67-93F6-3B4E17ED8491}">
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="15.85546875" style="17" customWidth="1"/>
+    <col min="2" max="2" width="15" style="17" customWidth="1"/>
     <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.5703125" style="17" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" style="17" customWidth="1"/>
     <col min="5" max="5" width="17.85546875" style="17" customWidth="1"/>
-    <col min="6" max="6" width="27" customWidth="1"/>
+    <col min="6" max="6" width="28.5703125" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.5703125" customWidth="1"/>
     <col min="9" max="9" width="21" style="27" customWidth="1"/>
@@ -3762,365 +3911,922 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="22"/>
+      <c r="B2" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="56">
+        <v>3450061791</v>
+      </c>
+      <c r="F2" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2" s="22" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="12"/>
+      <c r="B3" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="56">
+        <v>3450056181</v>
+      </c>
+      <c r="F3" s="58" t="s">
+        <v>125</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="22" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="12"/>
+      <c r="B4" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="56">
+        <v>3450058689</v>
+      </c>
+      <c r="F4" s="58" t="s">
+        <v>127</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="15"/>
+      <c r="B5" s="53" t="s">
+        <v>129</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="56">
+        <v>3450059866</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="9"/>
+      <c r="B6" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="56">
+        <v>3450062682</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="9"/>
+      <c r="B7" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="56">
+        <v>3450062385</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="9"/>
+      <c r="B8" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D8" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="56">
+        <v>3450064145</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="9"/>
+      <c r="B9" s="53">
+        <v>45883</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D9" s="57">
+        <v>133931478</v>
+      </c>
+      <c r="E9" s="18">
+        <v>3450053717</v>
+      </c>
+      <c r="F9" s="54" t="s">
+        <v>136</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="H9" s="59" t="s">
+        <v>138</v>
+      </c>
+      <c r="I9" s="27">
+        <v>45888</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="9"/>
+      <c r="B10" s="53">
+        <v>45888</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D10" s="57">
+        <v>134002781</v>
+      </c>
+      <c r="E10" s="18">
+        <v>3450057578</v>
+      </c>
+      <c r="F10" s="54" t="s">
+        <v>139</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I10" s="27">
+        <v>45888</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="9"/>
+      <c r="B11" s="53">
+        <v>45888</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D11" s="57">
+        <v>134011293</v>
+      </c>
+      <c r="E11" s="18">
+        <v>3450058282</v>
+      </c>
+      <c r="F11" s="54" t="s">
+        <v>140</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I11" s="27">
+        <v>45888</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="9"/>
+      <c r="B12" s="53">
+        <v>45888</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D12" s="57">
+        <v>134015104</v>
+      </c>
+      <c r="E12" s="18">
+        <v>3450058645</v>
+      </c>
+      <c r="F12" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I12" s="27">
+        <v>45888</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="9"/>
+      <c r="B13" s="53">
+        <v>45888</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13" s="57">
+        <v>134003094</v>
+      </c>
+      <c r="E13" s="18">
+        <v>3450057633</v>
+      </c>
+      <c r="F13" s="54" t="s">
+        <v>142</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I13" s="27">
+        <v>45888</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="9"/>
+      <c r="B14" s="53">
+        <v>45888</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D14" s="57">
+        <v>134009970</v>
+      </c>
+      <c r="E14" s="18">
+        <v>3450058150</v>
+      </c>
+      <c r="F14" s="54" t="s">
+        <v>143</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="59" t="s">
+        <v>144</v>
+      </c>
+      <c r="I14" s="27">
+        <v>45888</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="9"/>
+      <c r="B15" s="53">
+        <v>45889</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D15" s="57">
+        <v>134023812</v>
+      </c>
+      <c r="E15" s="18">
+        <v>3450058843</v>
+      </c>
+      <c r="F15" s="54" t="s">
+        <v>145</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="I15" s="27">
+        <v>45894</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="9"/>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="6"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="9"/>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="9"/>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="6"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="9"/>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="6"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="9"/>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="9"/>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="6"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="9"/>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="9"/>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="9"/>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="6"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="9"/>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="9"/>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="9"/>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="9"/>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="6"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="9"/>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="6"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="24"/>
-      <c r="H30" s="9"/>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="6"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="24"/>
-      <c r="H31" s="9"/>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="24"/>
-      <c r="H32" s="9"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="6"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="24"/>
-      <c r="H33" s="9"/>
-    </row>
-    <row r="34" spans="1:8">
+      <c r="B16" s="53">
+        <v>45888</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D16" s="57">
+        <v>134009993</v>
+      </c>
+      <c r="E16" s="18">
+        <v>3450058172</v>
+      </c>
+      <c r="F16" s="54" t="s">
+        <v>146</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I16" s="27">
+        <v>45888</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="53">
+        <v>45888</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D17" s="57">
+        <v>134015383</v>
+      </c>
+      <c r="E17" s="18">
+        <v>3450058667</v>
+      </c>
+      <c r="F17" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I17" s="27">
+        <v>45888</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="53">
+        <v>45922</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D18" s="57">
+        <v>134094458</v>
+      </c>
+      <c r="E18" s="18">
+        <v>3450062320</v>
+      </c>
+      <c r="F18" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="G18" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="I18" s="27">
+        <v>45895</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="53">
+        <v>45894</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D19" s="57">
+        <v>134095206</v>
+      </c>
+      <c r="E19" s="18">
+        <v>3450062352</v>
+      </c>
+      <c r="F19" s="54" t="s">
+        <v>150</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H19" s="59" t="s">
+        <v>35</v>
+      </c>
+      <c r="I19" s="27">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="53">
+        <v>45894</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D20" s="57">
+        <v>134111744</v>
+      </c>
+      <c r="E20" s="18">
+        <v>3450063474</v>
+      </c>
+      <c r="F20" s="54" t="s">
+        <v>151</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H20" s="59" t="s">
+        <v>35</v>
+      </c>
+      <c r="I20" s="27">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="53">
+        <v>45914</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D21" s="57">
+        <v>134106242</v>
+      </c>
+      <c r="E21" s="18">
+        <v>3450063090</v>
+      </c>
+      <c r="F21" s="54" t="s">
+        <v>152</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="I21" s="27">
+        <v>45896</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="53">
+        <v>45895</v>
+      </c>
+      <c r="C22" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D22" s="57">
+        <v>134131120</v>
+      </c>
+      <c r="E22" s="18">
+        <v>3450064673</v>
+      </c>
+      <c r="F22" s="54" t="s">
+        <v>153</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H22" s="59" t="s">
+        <v>35</v>
+      </c>
+      <c r="I22" s="27">
+        <v>45895</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="53">
+        <v>45888</v>
+      </c>
+      <c r="C23" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D23" s="57">
+        <v>134012774</v>
+      </c>
+      <c r="E23" s="18">
+        <v>3450058370</v>
+      </c>
+      <c r="F23" s="54" t="s">
+        <v>154</v>
+      </c>
+      <c r="G23" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23" s="59" t="s">
+        <v>155</v>
+      </c>
+      <c r="I23" s="27">
+        <v>45888</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="53">
+        <v>45898</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D24" s="57">
+        <v>134003887</v>
+      </c>
+      <c r="E24" s="18">
+        <v>3450057754</v>
+      </c>
+      <c r="F24" s="54" t="s">
+        <v>156</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="I24" s="27">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="53">
+        <v>45888</v>
+      </c>
+      <c r="C25" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D25" s="57">
+        <v>133996064</v>
+      </c>
+      <c r="E25" s="18">
+        <v>3450057281</v>
+      </c>
+      <c r="F25" s="54" t="s">
+        <v>157</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I25" s="27">
+        <v>45888</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="53">
+        <v>45888</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D26" s="57">
+        <v>134005385</v>
+      </c>
+      <c r="E26" s="18">
+        <v>3450057908</v>
+      </c>
+      <c r="F26" s="54" t="s">
+        <v>158</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I26" s="27">
+        <v>45888</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="53">
+        <v>45888</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D27" s="57">
+        <v>134007219</v>
+      </c>
+      <c r="E27" s="18">
+        <v>3450058018</v>
+      </c>
+      <c r="F27" s="54" t="s">
+        <v>159</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I27" s="27">
+        <v>45888</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="53">
+        <v>45888</v>
+      </c>
+      <c r="C28" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D28" s="57">
+        <v>134008340</v>
+      </c>
+      <c r="E28" s="18">
+        <v>3450058040</v>
+      </c>
+      <c r="F28" s="54" t="s">
+        <v>160</v>
+      </c>
+      <c r="G28" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I28" s="27">
+        <v>45888</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="53">
+        <v>45888</v>
+      </c>
+      <c r="C29" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D29" s="57">
+        <v>134009089</v>
+      </c>
+      <c r="E29" s="18">
+        <v>3450058084</v>
+      </c>
+      <c r="F29" s="54" t="s">
+        <v>161</v>
+      </c>
+      <c r="G29" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I29" s="27">
+        <v>45888</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="53">
+        <v>45888</v>
+      </c>
+      <c r="C30" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D30" s="57">
+        <v>134010861</v>
+      </c>
+      <c r="E30" s="18">
+        <v>3450058249</v>
+      </c>
+      <c r="F30" s="54" t="s">
+        <v>162</v>
+      </c>
+      <c r="G30" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I30" s="27">
+        <v>45888</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="53">
+        <v>45888</v>
+      </c>
+      <c r="C31" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D31" s="57">
+        <v>134011991</v>
+      </c>
+      <c r="E31" s="18">
+        <v>3450058348</v>
+      </c>
+      <c r="F31" s="54" t="s">
+        <v>163</v>
+      </c>
+      <c r="G31" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I31" s="27">
+        <v>45888</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="53">
+        <v>45888</v>
+      </c>
+      <c r="C32" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D32" s="57">
+        <v>134012545</v>
+      </c>
+      <c r="E32" s="18">
+        <v>3450058360</v>
+      </c>
+      <c r="F32" s="54" t="s">
+        <v>164</v>
+      </c>
+      <c r="G32" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I32" s="27">
+        <v>45888</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="53">
+        <v>45888</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D33" s="57">
+        <v>134015859</v>
+      </c>
+      <c r="E33" s="18">
+        <v>3450058700</v>
+      </c>
+      <c r="F33" s="54" t="s">
+        <v>165</v>
+      </c>
+      <c r="G33" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I33" s="27">
+        <v>45888</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" s="6"/>
-      <c r="B34" s="7"/>
+      <c r="B34" s="53"/>
       <c r="C34" s="28"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="12"/>
+      <c r="D34" s="47"/>
+      <c r="E34" s="48"/>
+      <c r="F34" s="36"/>
       <c r="G34" s="24"/>
       <c r="H34" s="9"/>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:9">
       <c r="A35" s="6"/>
-      <c r="B35" s="7"/>
+      <c r="B35" s="53"/>
       <c r="C35" s="28"/>
       <c r="D35" s="25"/>
       <c r="E35" s="18"/>
@@ -4128,27 +4834,27 @@
       <c r="G35" s="24"/>
       <c r="H35" s="9"/>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:9">
       <c r="A36" s="6"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="25"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="24"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="6"/>
       <c r="H36" s="9"/>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:9">
       <c r="A37" s="6"/>
       <c r="B37" s="8"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="15"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="9"/>
       <c r="G37" s="6"/>
       <c r="H37" s="9"/>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:9">
       <c r="A38" s="6"/>
       <c r="B38" s="8"/>
       <c r="C38" s="7"/>
@@ -4158,7 +4864,7 @@
       <c r="G38" s="6"/>
       <c r="H38" s="9"/>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:9">
       <c r="A39" s="6"/>
       <c r="B39" s="8"/>
       <c r="C39" s="7"/>
@@ -4168,7 +4874,7 @@
       <c r="G39" s="6"/>
       <c r="H39" s="9"/>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:9">
       <c r="A40" s="6"/>
       <c r="B40" s="8"/>
       <c r="C40" s="7"/>
@@ -4178,7 +4884,7 @@
       <c r="G40" s="6"/>
       <c r="H40" s="9"/>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:9">
       <c r="A41" s="6"/>
       <c r="B41" s="8"/>
       <c r="C41" s="7"/>
@@ -4188,7 +4894,7 @@
       <c r="G41" s="6"/>
       <c r="H41" s="9"/>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:9">
       <c r="A42" s="6"/>
       <c r="B42" s="8"/>
       <c r="C42" s="7"/>
@@ -4198,31 +4904,22 @@
       <c r="G42" s="6"/>
       <c r="H42" s="9"/>
     </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="6"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="9"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="7">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A17:A36" xr:uid="{F535CD1B-7EC8-4CD4-9DE2-4943F25AAD12}">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A33" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
+      <formula1>$J$2</formula1>
+    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2 B5:B30" xr:uid="{2960422A-53E1-48F0-9D55-C051B26376A4}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A34:A35" xr:uid="{F535CD1B-7EC8-4CD4-9DE2-4943F25AAD12}">
       <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G36" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G35" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:B16" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
-      <formula1>$J$2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6829,15 +7526,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -6887,9 +7575,9 @@
 </spe:Receivers>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="43" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="abf1b9912853fe4a934dbc2373304754">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d8d96f03b10d24171ef462918d18284e" ns1:_="" ns2:_="" ns3:_="">
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="43" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="32fbec5585ae01a22f32af5838af0c4d">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7b2552458edfdc024ce707f91c2c891f" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
     <xsd:import namespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea"/>
     <xsd:import namespace="ea6c6725-5210-4d6a-93cc-4cf85111ac5e"/>
@@ -6937,12 +7625,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Propriedades da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Ação de IU da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
@@ -6951,12 +7639,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Document ID Value" ma:description="The value of the document ID assigned to this item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
+    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Valor do ID do Documento" ma:description="O valor do ID do documento atribuído a este item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="Document ID" ma:description="Permanent link to this document." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
+    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="ID do Documento" ma:description="Ligação permanente a este documento." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:URL">
@@ -7039,7 +7727,7 @@
         <xsd:restriction base="dms:DateTime"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Partilhado Com" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -7058,7 +7746,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Detalhes de Partilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -7091,7 +7779,7 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de Imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -7169,8 +7857,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -7259,7 +7947,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-494894</_dlc_DocId>
@@ -7302,18 +7990,27 @@
 </p:properties>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99F7464B-B6DD-435B-A865-3332586D260B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098F1F3C-7054-44DA-97C1-1FA0AD811FFC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  25.08.2025 a 31.08.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  25.08.2025 a 31.08.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A9897DA-E3C6-4F84-A4A8-2F2CF258BD76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7895282-5B69-465C-9F73-245C78BE4D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="25.08" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="203">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -555,6 +555,127 @@
   </si>
   <si>
     <t xml:space="preserve">BRUNO VINICIUS ISAAC COSTA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLARISSA CRISTIANNE LESSA DOS SANTOS         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGNALDO CARO COLLETTI                        </t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 27.08.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIAGO CORREIA DE LIMA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: CHASSI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAMIRA ANDREA DA SILVA RAMOS                 </t>
+  </si>
+  <si>
+    <t>FOTO DO CHASSI/ LATERAL TRAS DIREITA., PRAZO EXPIRADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE MARCONI DE BARROS LIMA                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FABIOLA PALADINO MARTINS                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CELIA APARECIDA POLI MORELLI                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE CARLOS NERES DE ASSIS                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GILSON AURELIO LOPES ALVIM                   </t>
+  </si>
+  <si>
+    <t>Aceitação condicionada à confirmação de bônus na CBE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVONE ROSSI                                  </t>
+  </si>
+  <si>
+    <t>Informamos que o veículo da proposta em questão se encontra em dup
+licidade com uma apólice de outra corretagem com vigência até 17/0
+9/2024, para prosseguirmos com a emissão é necessário que o segura
+dosolicite o cancelamento e após poderá optar por realizar nova tr
+ansmissão como renovação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAIRO MANUEL CORDEIRO                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Santander - Bônus correto deve ser {}, favor corrigir.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RICARDO NORONHA DE ALMEIDA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PREVENCLIN LTDA EPP                          </t>
+  </si>
+  <si>
+    <t>SEGURADO NÃO CORRIGIU AS FOTOS / PRAZO INSPIRADO. Fotos que tiveram repique: Painel com a motocicleta ligada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRISTIANE ROCHA SARMENTO BARBOSA             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favor enviar cópia completa da apólice referente 2024/2025 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOURIVAL BARATA PENALBER NETO                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE LAZARONE EUFRASIO CORDEIRO              </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: Painel com carro ligado</t>
+  </si>
+  <si>
+    <t>FRUSTRADO, FOTOS NÃO CORRIGIDAS: Frente e lateral do passageiro e do motorista, Traseira e lateral do motorista e do passageiro, Painel com carro ligado,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NELSON ROBERTO GENNARI JUNIOR                </t>
+  </si>
+  <si>
+    <t>C
+onforme CBE houve quebra de vigência de 125 dias e não houve sinis
+tro (Renovação externa sem sinistro), conforme regra reduz quatro
+classes de bônus, assim sendo o correto bônus  0</t>
+  </si>
+  <si>
+    <t>L W EXPRESS TRANSPORTES RODOVIARIOS EXPRESSOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WENDELL LUCAS LIMA DE SOUSA                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULO VICTOR ARAUJO DOS SANTOS               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCIANO SOUSA RETAMIRO                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIH NEGOCIOS COMERCIO E SERVICOS LTDA ME     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCENARIA S R J LTDA ME                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDERSON JOSE DA SILVA                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCOS ROBERTO MENDES                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conforme consulta na central de bônus, identificamos que não
+há possibilidade efetuar a transferência de bônus para o(a) senho
+r(a) MARCOS ROBERTO MENDES , pois este não consta como condutor na
+apólice anterior. </t>
   </si>
 </sst>
 </file>
@@ -935,17 +1056,19 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -3920,10 +4043,10 @@
       <c r="D2" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="56">
+      <c r="E2" s="55">
         <v>3450061791</v>
       </c>
-      <c r="F2" s="58" t="s">
+      <c r="F2" s="12" t="s">
         <v>122</v>
       </c>
       <c r="G2" s="20" t="s">
@@ -3946,10 +4069,10 @@
       <c r="D3" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="56">
+      <c r="E3" s="55">
         <v>3450056181</v>
       </c>
-      <c r="F3" s="58" t="s">
+      <c r="F3" s="12" t="s">
         <v>125</v>
       </c>
       <c r="G3" s="20" t="s">
@@ -3972,10 +4095,10 @@
       <c r="D4" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="56">
+      <c r="E4" s="55">
         <v>3450058689</v>
       </c>
-      <c r="F4" s="58" t="s">
+      <c r="F4" s="12" t="s">
         <v>127</v>
       </c>
       <c r="G4" s="20" t="s">
@@ -3998,7 +4121,7 @@
       <c r="D5" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="56">
+      <c r="E5" s="55">
         <v>3450059866</v>
       </c>
       <c r="F5" s="12" t="s">
@@ -4024,7 +4147,7 @@
       <c r="D6" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="56">
+      <c r="E6" s="55">
         <v>3450062682</v>
       </c>
       <c r="F6" s="12" t="s">
@@ -4050,7 +4173,7 @@
       <c r="D7" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="56">
+      <c r="E7" s="55">
         <v>3450062385</v>
       </c>
       <c r="F7" s="12" t="s">
@@ -4073,10 +4196,10 @@
       <c r="C8" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="D8" s="55" t="s">
+      <c r="D8" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="56">
+      <c r="E8" s="55">
         <v>3450064145</v>
       </c>
       <c r="F8" s="31" t="s">
@@ -4099,19 +4222,19 @@
       <c r="C9" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="D9" s="57">
+      <c r="D9" s="25">
         <v>133931478</v>
       </c>
       <c r="E9" s="18">
         <v>3450053717</v>
       </c>
-      <c r="F9" s="54" t="s">
+      <c r="F9" s="12" t="s">
         <v>136</v>
       </c>
       <c r="G9" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="H9" s="59" t="s">
+      <c r="H9" s="9" t="s">
         <v>138</v>
       </c>
       <c r="I9" s="27">
@@ -4128,13 +4251,13 @@
       <c r="C10" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="D10" s="57">
+      <c r="D10" s="25">
         <v>134002781</v>
       </c>
       <c r="E10" s="18">
         <v>3450057578</v>
       </c>
-      <c r="F10" s="54" t="s">
+      <c r="F10" s="12" t="s">
         <v>139</v>
       </c>
       <c r="G10" s="24" t="s">
@@ -4157,13 +4280,13 @@
       <c r="C11" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="D11" s="57">
+      <c r="D11" s="25">
         <v>134011293</v>
       </c>
       <c r="E11" s="18">
         <v>3450058282</v>
       </c>
-      <c r="F11" s="54" t="s">
+      <c r="F11" s="12" t="s">
         <v>140</v>
       </c>
       <c r="G11" s="20" t="s">
@@ -4186,13 +4309,13 @@
       <c r="C12" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="D12" s="57">
+      <c r="D12" s="25">
         <v>134015104</v>
       </c>
       <c r="E12" s="18">
         <v>3450058645</v>
       </c>
-      <c r="F12" s="54" t="s">
+      <c r="F12" s="12" t="s">
         <v>141</v>
       </c>
       <c r="G12" s="24" t="s">
@@ -4215,13 +4338,13 @@
       <c r="C13" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="D13" s="57">
+      <c r="D13" s="25">
         <v>134003094</v>
       </c>
       <c r="E13" s="18">
         <v>3450057633</v>
       </c>
-      <c r="F13" s="54" t="s">
+      <c r="F13" s="12" t="s">
         <v>142</v>
       </c>
       <c r="G13" s="20" t="s">
@@ -4244,19 +4367,19 @@
       <c r="C14" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="D14" s="57">
+      <c r="D14" s="25">
         <v>134009970</v>
       </c>
       <c r="E14" s="18">
         <v>3450058150</v>
       </c>
-      <c r="F14" s="54" t="s">
+      <c r="F14" s="12" t="s">
         <v>143</v>
       </c>
       <c r="G14" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H14" s="59" t="s">
+      <c r="H14" s="9" t="s">
         <v>144</v>
       </c>
       <c r="I14" s="27">
@@ -4273,13 +4396,13 @@
       <c r="C15" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="D15" s="57">
+      <c r="D15" s="25">
         <v>134023812</v>
       </c>
       <c r="E15" s="18">
         <v>3450058843</v>
       </c>
-      <c r="F15" s="54" t="s">
+      <c r="F15" s="12" t="s">
         <v>145</v>
       </c>
       <c r="G15" s="20" t="s">
@@ -4302,13 +4425,13 @@
       <c r="C16" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="D16" s="57">
+      <c r="D16" s="25">
         <v>134009993</v>
       </c>
       <c r="E16" s="18">
         <v>3450058172</v>
       </c>
-      <c r="F16" s="54" t="s">
+      <c r="F16" s="12" t="s">
         <v>146</v>
       </c>
       <c r="G16" s="20" t="s">
@@ -4331,13 +4454,13 @@
       <c r="C17" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="D17" s="57">
+      <c r="D17" s="25">
         <v>134015383</v>
       </c>
       <c r="E17" s="18">
         <v>3450058667</v>
       </c>
-      <c r="F17" s="54" t="s">
+      <c r="F17" s="12" t="s">
         <v>147</v>
       </c>
       <c r="G17" s="20" t="s">
@@ -4360,13 +4483,13 @@
       <c r="C18" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="D18" s="57">
+      <c r="D18" s="25">
         <v>134094458</v>
       </c>
       <c r="E18" s="18">
         <v>3450062320</v>
       </c>
-      <c r="F18" s="54" t="s">
+      <c r="F18" s="12" t="s">
         <v>148</v>
       </c>
       <c r="G18" s="24" t="s">
@@ -4389,19 +4512,19 @@
       <c r="C19" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="D19" s="57">
+      <c r="D19" s="25">
         <v>134095206</v>
       </c>
       <c r="E19" s="18">
         <v>3450062352</v>
       </c>
-      <c r="F19" s="54" t="s">
+      <c r="F19" s="12" t="s">
         <v>150</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="H19" s="59" t="s">
+      <c r="H19" s="9" t="s">
         <v>35</v>
       </c>
       <c r="I19" s="27">
@@ -4418,19 +4541,19 @@
       <c r="C20" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="D20" s="57">
+      <c r="D20" s="25">
         <v>134111744</v>
       </c>
       <c r="E20" s="18">
         <v>3450063474</v>
       </c>
-      <c r="F20" s="54" t="s">
+      <c r="F20" s="12" t="s">
         <v>151</v>
       </c>
       <c r="G20" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="H20" s="59" t="s">
+      <c r="H20" s="9" t="s">
         <v>35</v>
       </c>
       <c r="I20" s="27">
@@ -4447,13 +4570,13 @@
       <c r="C21" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="D21" s="57">
+      <c r="D21" s="25">
         <v>134106242</v>
       </c>
       <c r="E21" s="18">
         <v>3450063090</v>
       </c>
-      <c r="F21" s="54" t="s">
+      <c r="F21" s="12" t="s">
         <v>152</v>
       </c>
       <c r="G21" s="20" t="s">
@@ -4476,19 +4599,19 @@
       <c r="C22" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="D22" s="57">
+      <c r="D22" s="25">
         <v>134131120</v>
       </c>
       <c r="E22" s="18">
         <v>3450064673</v>
       </c>
-      <c r="F22" s="54" t="s">
+      <c r="F22" s="12" t="s">
         <v>153</v>
       </c>
       <c r="G22" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="H22" s="59" t="s">
+      <c r="H22" s="9" t="s">
         <v>35</v>
       </c>
       <c r="I22" s="27">
@@ -4505,19 +4628,19 @@
       <c r="C23" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="D23" s="57">
+      <c r="D23" s="25">
         <v>134012774</v>
       </c>
       <c r="E23" s="18">
         <v>3450058370</v>
       </c>
-      <c r="F23" s="54" t="s">
+      <c r="F23" s="12" t="s">
         <v>154</v>
       </c>
       <c r="G23" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="H23" s="59" t="s">
+      <c r="H23" s="9" t="s">
         <v>155</v>
       </c>
       <c r="I23" s="27">
@@ -4534,13 +4657,13 @@
       <c r="C24" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="D24" s="57">
+      <c r="D24" s="25">
         <v>134003887</v>
       </c>
       <c r="E24" s="18">
         <v>3450057754</v>
       </c>
-      <c r="F24" s="54" t="s">
+      <c r="F24" s="12" t="s">
         <v>156</v>
       </c>
       <c r="G24" s="20" t="s">
@@ -4563,13 +4686,13 @@
       <c r="C25" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="D25" s="57">
+      <c r="D25" s="25">
         <v>133996064</v>
       </c>
       <c r="E25" s="18">
         <v>3450057281</v>
       </c>
-      <c r="F25" s="54" t="s">
+      <c r="F25" s="12" t="s">
         <v>157</v>
       </c>
       <c r="G25" s="20" t="s">
@@ -4592,13 +4715,13 @@
       <c r="C26" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="D26" s="57">
+      <c r="D26" s="25">
         <v>134005385</v>
       </c>
       <c r="E26" s="18">
         <v>3450057908</v>
       </c>
-      <c r="F26" s="54" t="s">
+      <c r="F26" s="12" t="s">
         <v>158</v>
       </c>
       <c r="G26" s="20" t="s">
@@ -4621,13 +4744,13 @@
       <c r="C27" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="D27" s="57">
+      <c r="D27" s="25">
         <v>134007219</v>
       </c>
       <c r="E27" s="18">
         <v>3450058018</v>
       </c>
-      <c r="F27" s="54" t="s">
+      <c r="F27" s="12" t="s">
         <v>159</v>
       </c>
       <c r="G27" s="20" t="s">
@@ -4650,13 +4773,13 @@
       <c r="C28" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="D28" s="57">
+      <c r="D28" s="25">
         <v>134008340</v>
       </c>
       <c r="E28" s="18">
         <v>3450058040</v>
       </c>
-      <c r="F28" s="54" t="s">
+      <c r="F28" s="12" t="s">
         <v>160</v>
       </c>
       <c r="G28" s="24" t="s">
@@ -4679,13 +4802,13 @@
       <c r="C29" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="D29" s="57">
+      <c r="D29" s="25">
         <v>134009089</v>
       </c>
       <c r="E29" s="18">
         <v>3450058084</v>
       </c>
-      <c r="F29" s="54" t="s">
+      <c r="F29" s="12" t="s">
         <v>161</v>
       </c>
       <c r="G29" s="24" t="s">
@@ -4708,13 +4831,13 @@
       <c r="C30" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="D30" s="57">
+      <c r="D30" s="25">
         <v>134010861</v>
       </c>
       <c r="E30" s="18">
         <v>3450058249</v>
       </c>
-      <c r="F30" s="54" t="s">
+      <c r="F30" s="12" t="s">
         <v>162</v>
       </c>
       <c r="G30" s="24" t="s">
@@ -4737,13 +4860,13 @@
       <c r="C31" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="D31" s="57">
+      <c r="D31" s="25">
         <v>134011991</v>
       </c>
       <c r="E31" s="18">
         <v>3450058348</v>
       </c>
-      <c r="F31" s="54" t="s">
+      <c r="F31" s="12" t="s">
         <v>163</v>
       </c>
       <c r="G31" s="24" t="s">
@@ -4766,13 +4889,13 @@
       <c r="C32" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="D32" s="57">
+      <c r="D32" s="25">
         <v>134012545</v>
       </c>
       <c r="E32" s="18">
         <v>3450058360</v>
       </c>
-      <c r="F32" s="54" t="s">
+      <c r="F32" s="12" t="s">
         <v>164</v>
       </c>
       <c r="G32" s="24" t="s">
@@ -4795,13 +4918,13 @@
       <c r="C33" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="D33" s="57">
+      <c r="D33" s="25">
         <v>134015859</v>
       </c>
       <c r="E33" s="18">
         <v>3450058700</v>
       </c>
-      <c r="F33" s="54" t="s">
+      <c r="F33" s="12" t="s">
         <v>165</v>
       </c>
       <c r="G33" s="24" t="s">
@@ -4928,17 +5051,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BF216D7-F2B3-4C54-A7B9-7048B06C2C75}">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.28515625" customWidth="1"/>
     <col min="2" max="2" width="15.5703125" customWidth="1"/>
     <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" customWidth="1"/>
     <col min="6" max="6" width="36.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.42578125" customWidth="1"/>
     <col min="9" max="9" width="18.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4971,330 +5094,796 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" ht="29.25">
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="27"/>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="B2" s="7">
+        <v>45889</v>
+      </c>
+      <c r="C2" s="28">
+        <v>45897</v>
+      </c>
+      <c r="D2" s="57">
+        <v>134037866</v>
+      </c>
+      <c r="E2" s="18">
+        <v>3450059690</v>
+      </c>
+      <c r="F2" s="56" t="s">
+        <v>166</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="27">
+        <v>45889</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="29.25">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="27"/>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="B3" s="7">
+        <v>45889</v>
+      </c>
+      <c r="C3" s="28">
+        <v>45897</v>
+      </c>
+      <c r="D3" s="57">
+        <v>134030410</v>
+      </c>
+      <c r="E3" s="18">
+        <v>3450059140</v>
+      </c>
+      <c r="F3" s="58" t="s">
+        <v>167</v>
+      </c>
+      <c r="G3" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3" s="59" t="s">
+        <v>168</v>
+      </c>
+      <c r="I3" s="27">
+        <v>45896</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="29.25">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="27"/>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="B4" s="7">
+        <v>45891</v>
+      </c>
+      <c r="C4" s="28">
+        <v>45897</v>
+      </c>
+      <c r="D4" s="57">
+        <v>134085449</v>
+      </c>
+      <c r="E4" s="18">
+        <v>3450062100</v>
+      </c>
+      <c r="F4" s="58" t="s">
+        <v>169</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="59" t="s">
+        <v>170</v>
+      </c>
+      <c r="I4" s="27">
+        <v>45891</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="29.25">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="27"/>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="B5" s="7">
+        <v>45891</v>
+      </c>
+      <c r="C5" s="28">
+        <v>45897</v>
+      </c>
+      <c r="D5" s="57">
+        <v>134081882</v>
+      </c>
+      <c r="E5" s="18">
+        <v>3450061769</v>
+      </c>
+      <c r="F5" s="58" t="s">
+        <v>171</v>
+      </c>
+      <c r="G5" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="59" t="s">
+        <v>172</v>
+      </c>
+      <c r="I5" s="27">
+        <v>45891</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="29.25">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="27"/>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="B6" s="7">
+        <v>45906</v>
+      </c>
+      <c r="C6" s="28">
+        <v>45897</v>
+      </c>
+      <c r="D6" s="57">
+        <v>134120327</v>
+      </c>
+      <c r="E6" s="18">
+        <v>3450063848</v>
+      </c>
+      <c r="F6" s="58" t="s">
+        <v>173</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="59" t="s">
+        <v>168</v>
+      </c>
+      <c r="I6" s="27">
+        <v>45896</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="29.25">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="27"/>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="B7" s="7">
+        <v>45905</v>
+      </c>
+      <c r="C7" s="28">
+        <v>45897</v>
+      </c>
+      <c r="D7" s="57">
+        <v>134123005</v>
+      </c>
+      <c r="E7" s="18">
+        <v>3450064090</v>
+      </c>
+      <c r="F7" s="58" t="s">
+        <v>174</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="59" t="s">
+        <v>168</v>
+      </c>
+      <c r="I7" s="27">
+        <v>45896</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="29.25">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="27"/>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="B8" s="7">
+        <v>45896</v>
+      </c>
+      <c r="C8" s="28">
+        <v>45897</v>
+      </c>
+      <c r="D8" s="57">
+        <v>134151226</v>
+      </c>
+      <c r="E8" s="18">
+        <v>3450065828</v>
+      </c>
+      <c r="F8" s="58" t="s">
+        <v>175</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" s="59" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" s="27">
+        <v>45896</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="29.25">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="27"/>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="B9" s="7">
+        <v>45891</v>
+      </c>
+      <c r="C9" s="28">
+        <v>45897</v>
+      </c>
+      <c r="D9" s="57">
+        <v>134156211</v>
+      </c>
+      <c r="E9" s="18">
+        <v>3450062121</v>
+      </c>
+      <c r="F9" s="58" t="s">
+        <v>176</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9" s="59" t="s">
+        <v>35</v>
+      </c>
+      <c r="I9" s="27">
+        <v>45891</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="29.25">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="27"/>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="B10" s="7">
+        <v>45884</v>
+      </c>
+      <c r="C10" s="28">
+        <v>45897</v>
+      </c>
+      <c r="D10" s="57">
+        <v>133953737</v>
+      </c>
+      <c r="E10" s="18">
+        <v>3450054916</v>
+      </c>
+      <c r="F10" s="58" t="s">
+        <v>177</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="59" t="s">
+        <v>178</v>
+      </c>
+      <c r="I10" s="27">
+        <v>45884</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="29.25">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="27"/>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="B11" s="7">
+        <v>45884</v>
+      </c>
+      <c r="C11" s="28">
+        <v>45897</v>
+      </c>
+      <c r="D11" s="57">
+        <v>133956942</v>
+      </c>
+      <c r="E11" s="18">
+        <v>3450055213</v>
+      </c>
+      <c r="F11" s="58" t="s">
+        <v>179</v>
+      </c>
+      <c r="G11" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" s="59" t="s">
+        <v>106</v>
+      </c>
+      <c r="I11" s="27">
+        <v>45889</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="29.25">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="27"/>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="B12" s="7">
+        <v>45884</v>
+      </c>
+      <c r="C12" s="28">
+        <v>45897</v>
+      </c>
+      <c r="D12" s="57">
+        <v>133957208</v>
+      </c>
+      <c r="E12" s="18">
+        <v>3450055268</v>
+      </c>
+      <c r="F12" s="58" t="s">
+        <v>171</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" s="59" t="s">
+        <v>180</v>
+      </c>
+      <c r="I12" s="27">
+        <v>45884</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="29.25">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="27"/>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="B13" s="7">
+        <v>45884</v>
+      </c>
+      <c r="C13" s="28">
+        <v>45897</v>
+      </c>
+      <c r="D13" s="57">
+        <v>133969078</v>
+      </c>
+      <c r="E13" s="18">
+        <v>3450056060</v>
+      </c>
+      <c r="F13" s="58" t="s">
+        <v>181</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="59" t="s">
+        <v>182</v>
+      </c>
+      <c r="I13" s="27">
+        <v>45884</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="29.25">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="27"/>
-    </row>
-    <row r="15" spans="1:9">
+      <c r="B14" s="7">
+        <v>45905</v>
+      </c>
+      <c r="C14" s="28">
+        <v>45897</v>
+      </c>
+      <c r="D14" s="57">
+        <v>133968156</v>
+      </c>
+      <c r="E14" s="18">
+        <v>3450056049</v>
+      </c>
+      <c r="F14" s="58" t="s">
+        <v>183</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="H14" s="59" t="s">
+        <v>168</v>
+      </c>
+      <c r="I14" s="27">
+        <v>45896</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="29.25">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="27"/>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="6"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="27"/>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="6"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="27"/>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="27"/>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="27"/>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="27"/>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="9"/>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="9"/>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="9"/>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="9"/>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="9"/>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="9"/>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="9"/>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="9"/>
+      <c r="B15" s="7">
+        <v>45889</v>
+      </c>
+      <c r="C15" s="28">
+        <v>45897</v>
+      </c>
+      <c r="D15" s="57">
+        <v>134028341</v>
+      </c>
+      <c r="E15" s="18">
+        <v>3450059030</v>
+      </c>
+      <c r="F15" s="58" t="s">
+        <v>184</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" s="59" t="s">
+        <v>185</v>
+      </c>
+      <c r="I15" s="27">
+        <v>45889</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="29.25">
+      <c r="A16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="7">
+        <v>45890</v>
+      </c>
+      <c r="C16" s="28">
+        <v>45897</v>
+      </c>
+      <c r="D16" s="57">
+        <v>133980074</v>
+      </c>
+      <c r="E16" s="18">
+        <v>3450056478</v>
+      </c>
+      <c r="F16" s="58" t="s">
+        <v>186</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="59" t="s">
+        <v>187</v>
+      </c>
+      <c r="I16" s="27">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="29.25">
+      <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="7">
+        <v>45890</v>
+      </c>
+      <c r="C17" s="28">
+        <v>45897</v>
+      </c>
+      <c r="D17" s="57">
+        <v>134046643</v>
+      </c>
+      <c r="E17" s="18">
+        <v>3450059987</v>
+      </c>
+      <c r="F17" s="58" t="s">
+        <v>188</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H17" s="59" t="s">
+        <v>35</v>
+      </c>
+      <c r="I17" s="27">
+        <v>45890</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="29.25">
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="7">
+        <v>45889</v>
+      </c>
+      <c r="C18" s="28">
+        <v>45897</v>
+      </c>
+      <c r="D18" s="57">
+        <v>134021045</v>
+      </c>
+      <c r="E18" s="18">
+        <v>3450058744</v>
+      </c>
+      <c r="F18" s="58" t="s">
+        <v>189</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" s="59" t="s">
+        <v>190</v>
+      </c>
+      <c r="I18" s="27">
+        <v>45889</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="29.25">
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>45889</v>
+      </c>
+      <c r="C19" s="28">
+        <v>45897</v>
+      </c>
+      <c r="D19" s="57">
+        <v>134028122</v>
+      </c>
+      <c r="E19" s="18">
+        <v>3450059019</v>
+      </c>
+      <c r="F19" s="58" t="s">
+        <v>184</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" s="59" t="s">
+        <v>191</v>
+      </c>
+      <c r="I19" s="27">
+        <v>45889</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="29.25">
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>45884</v>
+      </c>
+      <c r="C20" s="28">
+        <v>45897</v>
+      </c>
+      <c r="D20" s="57">
+        <v>133961625</v>
+      </c>
+      <c r="E20" s="18">
+        <v>3450055521</v>
+      </c>
+      <c r="F20" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" s="59" t="s">
+        <v>193</v>
+      </c>
+      <c r="I20" s="27">
+        <v>45889</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="29.25">
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>45889</v>
+      </c>
+      <c r="C21" s="28">
+        <v>45897</v>
+      </c>
+      <c r="D21" s="57">
+        <v>134026947</v>
+      </c>
+      <c r="E21" s="18">
+        <v>3450058920</v>
+      </c>
+      <c r="F21" s="56" t="s">
+        <v>194</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" s="27">
+        <v>45889</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="29.25">
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>45889</v>
+      </c>
+      <c r="C22" s="28">
+        <v>45897</v>
+      </c>
+      <c r="D22" s="57">
+        <v>134027915</v>
+      </c>
+      <c r="E22" s="18">
+        <v>3450058975</v>
+      </c>
+      <c r="F22" s="58" t="s">
+        <v>195</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" s="27">
+        <v>45889</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="29.25">
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>45889</v>
+      </c>
+      <c r="C23" s="28">
+        <v>45897</v>
+      </c>
+      <c r="D23" s="57">
+        <v>134027953</v>
+      </c>
+      <c r="E23" s="18">
+        <v>3450058975</v>
+      </c>
+      <c r="F23" s="58" t="s">
+        <v>196</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I23" s="27">
+        <v>45889</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="29.25">
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>45889</v>
+      </c>
+      <c r="C24" s="28">
+        <v>45897</v>
+      </c>
+      <c r="D24" s="57">
+        <v>134029327</v>
+      </c>
+      <c r="E24" s="18">
+        <v>3450059107</v>
+      </c>
+      <c r="F24" s="58" t="s">
+        <v>197</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I24" s="27">
+        <v>45889</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="29.25">
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>45889</v>
+      </c>
+      <c r="C25" s="28">
+        <v>45897</v>
+      </c>
+      <c r="D25" s="57">
+        <v>134033569</v>
+      </c>
+      <c r="E25" s="18">
+        <v>3450059393</v>
+      </c>
+      <c r="F25" s="56" t="s">
+        <v>198</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I25" s="27">
+        <v>45889</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="29.25">
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="7">
+        <v>45889</v>
+      </c>
+      <c r="C26" s="28">
+        <v>45897</v>
+      </c>
+      <c r="D26" s="57">
+        <v>134033796</v>
+      </c>
+      <c r="E26" s="18">
+        <v>3450059404</v>
+      </c>
+      <c r="F26" s="58" t="s">
+        <v>199</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I26" s="27">
+        <v>45889</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="29.25">
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="7">
+        <v>45889</v>
+      </c>
+      <c r="C27" s="28">
+        <v>45897</v>
+      </c>
+      <c r="D27" s="57">
+        <v>134037774</v>
+      </c>
+      <c r="E27" s="18">
+        <v>3450059679</v>
+      </c>
+      <c r="F27" s="58" t="s">
+        <v>200</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27" s="27">
+        <v>45889</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="29.25">
+      <c r="A28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="7">
+        <v>45894</v>
+      </c>
+      <c r="C28" s="28">
+        <v>45897</v>
+      </c>
+      <c r="D28" s="57">
+        <v>134075647</v>
+      </c>
+      <c r="E28" s="18">
+        <v>3450061406</v>
+      </c>
+      <c r="F28" s="58" t="s">
+        <v>201</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="H28" s="59" t="s">
+        <v>202</v>
+      </c>
+      <c r="I28" s="27">
+        <v>45897</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6"/>
       <c r="B29" s="8"/>
       <c r="C29" s="7"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="9"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="15"/>
       <c r="G29" s="6"/>
       <c r="H29" s="9"/>
     </row>
@@ -5518,57 +6107,17 @@
       <c r="G51" s="6"/>
       <c r="H51" s="9"/>
     </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="6"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="9"/>
-    </row>
-    <row r="53" spans="1:8">
-      <c r="A53" s="6"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="9"/>
-    </row>
-    <row r="54" spans="1:8">
-      <c r="A54" s="6"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="9"/>
-    </row>
-    <row r="55" spans="1:8">
-      <c r="A55" s="6"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="9"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="3">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{69840FBE-03D6-48CB-B553-2E7186E1B4BD}">
-      <formula1>$J$2</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A28" xr:uid="{69840FBE-03D6-48CB-B553-2E7186E1B4BD}">
+      <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{AF5C7196-9DAE-4339-82D4-9412023E2B2A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G37" xr:uid="{AF5C7196-9DAE-4339-82D4-9412023E2B2A}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7526,58 +8075,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="43" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="32fbec5585ae01a22f32af5838af0c4d">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7b2552458edfdc024ce707f91c2c891f" ns1:_="" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="43" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="abf1b9912853fe4a934dbc2373304754">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d8d96f03b10d24171ef462918d18284e" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
     <xsd:import namespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea"/>
     <xsd:import namespace="ea6c6725-5210-4d6a-93cc-4cf85111ac5e"/>
@@ -7625,12 +8124,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Propriedades da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="23" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Ação de IU da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="24" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
@@ -7639,12 +8138,12 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Valor do ID do Documento" ma:description="O valor do ID do documento atribuído a este item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
+    <xsd:element name="_dlc_DocId" ma:index="8" nillable="true" ma:displayName="Document ID Value" ma:description="The value of the document ID assigned to this item." ma:indexed="true" ma:internalName="_dlc_DocId" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="ID do Documento" ma:description="Ligação permanente a este documento." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
+    <xsd:element name="_dlc_DocIdUrl" ma:index="9" nillable="true" ma:displayName="Document ID" ma:description="Permanent link to this document." ma:hidden="true" ma:internalName="_dlc_DocIdUrl" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:URL">
@@ -7727,7 +8226,7 @@
         <xsd:restriction base="dms:DateTime"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Partilhado Com" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -7746,7 +8245,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Detalhes de Partilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -7779,7 +8278,7 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de Imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="26" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="10820af1-e82f-496e-bbcb-d9502914b7b2" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -7857,8 +8356,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -7947,7 +8446,66 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-494894</_dlc_DocId>
@@ -7990,27 +8548,18 @@
 </p:properties>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F38E076B-DE6E-4067-90F8-8ED2CC8B8C04}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99F7464B-B6DD-435B-A865-3332586D260B}"/>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  25.08.2025 a 31.08.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  25.08.2025 a 31.08.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7895282-5B69-465C-9F73-245C78BE4D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{60693BFB-FD26-4121-A28A-4237E24A637E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="25.08" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="239">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -676,6 +676,128 @@
 há possibilidade efetuar a transferência de bônus para o(a) senho
 r(a) MARCOS ROBERTO MENDES , pois este não consta como condutor na
 apólice anterior. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLEBER ANTONIO BATISTA DE OLIVEIRA ALONSO    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SARSON RENER CUSTODIO DE OLIVEIRA            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSILENE BARBOSA DA SILVA                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIE ELISABETH KORANYI MARTINS RIBEIRO      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIMAS FLORENTINO DO NASCIMENTO               </t>
+  </si>
+  <si>
+    <t>NUP Cancelamento 28.08.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANA DE FATIMA RIBEIRO RAMOS                  </t>
+  </si>
+  <si>
+    <t>Duplicidade com a proposta 134057758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSEMARI DOS PASSOS BRANDAO                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conforme consulta na central de bônus, identificamos que não
+há possibilidade efetuar a transferência de bônus para o(a) senho
+r(a) ROSEMARI DOS PASSOS BRANDAO, pois este não consta como condut
+or na apólice anterior. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCIANE GOMES                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JULIO CESAR PEREIRA FERRAZ DO PRADO          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE DE FREITAS VIEIRA                       </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, a apólice foi renovada na
+congênere de origem. Portanto, peço a gentileza de encaminhar a d
+ocumentação abaixo para análise:Cópia da apólice congênere c
+om vigência de 2025 a 2026;Endosso de cancelamento emitido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EOLO DE CAMARGO PRETO NETO                   </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, a apólice foi renovada na
+congênere de origem, portanto peço a gentileza de encaminhar a do
+cumentação abaixo, para análise.&lt;br&gt;Cópia da apólice congênere com
+vigência de 2025 à 2026 e Endosso de cancelamento emitido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HENRIQUE CALLIMAN VIANA                      </t>
+  </si>
+  <si>
+    <t>A apólice enviada foi cancelada na congênere em 23/08/2024, caso n
+ão possua apólice com vigência atual será necessário realizar nova
+transmissão como seguro novo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERNANDO FLORENTINO DA SILVA                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALESSANDRA VIANA TEIXEIRA                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALBERTINO BELARMINO BARBOSA NETO             </t>
+  </si>
+  <si>
+    <t>para que possamos prosseguir
+com a liberação do bloqueio será necessário a apresentação do en
+dosso de cancelamento emitido,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIOVANI VIEIRA LIMA                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIRES SOUZA MACIEL ME                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAPHAEL DA SILVA CARDOSO                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Santander - Veículo em duplicidade com proposta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JEANE DIAS DA SILVA                          </t>
+  </si>
+  <si>
+    <t>PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: Documento do veículo, Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCISCO FREIRE DE SOUZA                    </t>
+  </si>
+  <si>
+    <t>PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAUDEMIR ALVES DA SILVA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PABLO PORTO DA SILVA                         </t>
+  </si>
+  <si>
+    <t>Favor enviar cópia do endosso de cancelamento da apólice 2025/202
+6 através desse e-mail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADRIANO JOSE DA SILVA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVANI DA COSTA ALVES                         </t>
+  </si>
+  <si>
+    <t>PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: Frente e lateral do passageiro, Frente e lateral do motorista, Chassi</t>
   </si>
 </sst>
 </file>
@@ -921,7 +1043,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1013,7 +1135,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1066,16 +1187,29 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_Plan2_1" xfId="1" xr:uid="{69F13A52-20D9-46CA-8619-BC7A1BA09FD8}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2553,9 +2687,9 @@
       <c r="A40" s="6"/>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
-      <c r="D40" s="47"/>
-      <c r="E40" s="48"/>
-      <c r="F40" s="49"/>
+      <c r="D40" s="46"/>
+      <c r="E40" s="47"/>
+      <c r="F40" s="48"/>
       <c r="G40" s="20"/>
       <c r="H40" s="9"/>
       <c r="I40" s="27"/>
@@ -2821,7 +2955,7 @@
       <c r="C3" s="28">
         <v>45895</v>
       </c>
-      <c r="D3" s="52" t="s">
+      <c r="D3" s="51" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="18">
@@ -2851,7 +2985,7 @@
       <c r="D4" s="25">
         <v>133978332</v>
       </c>
-      <c r="E4" s="50">
+      <c r="E4" s="49">
         <v>3450054113</v>
       </c>
       <c r="F4" s="12" t="s">
@@ -2880,7 +3014,7 @@
       <c r="D5" s="25">
         <v>133981283</v>
       </c>
-      <c r="E5" s="50">
+      <c r="E5" s="49">
         <v>3450055202</v>
       </c>
       <c r="F5" s="12" t="s">
@@ -2909,7 +3043,7 @@
       <c r="D6" s="25">
         <v>133985758</v>
       </c>
-      <c r="E6" s="50">
+      <c r="E6" s="49">
         <v>3450056775</v>
       </c>
       <c r="F6" s="12" t="s">
@@ -2938,7 +3072,7 @@
       <c r="D7" s="25">
         <v>133980027</v>
       </c>
-      <c r="E7" s="50">
+      <c r="E7" s="49">
         <v>3450055884</v>
       </c>
       <c r="F7" s="12" t="s">
@@ -2967,7 +3101,7 @@
       <c r="D8" s="25">
         <v>134028037</v>
       </c>
-      <c r="E8" s="50">
+      <c r="E8" s="49">
         <v>3450058997</v>
       </c>
       <c r="F8" s="12" t="s">
@@ -2996,7 +3130,7 @@
       <c r="D9" s="25">
         <v>134062392</v>
       </c>
-      <c r="E9" s="50">
+      <c r="E9" s="49">
         <v>3450060768</v>
       </c>
       <c r="F9" s="12" t="s">
@@ -3025,7 +3159,7 @@
       <c r="D10" s="25">
         <v>133976697</v>
       </c>
-      <c r="E10" s="50">
+      <c r="E10" s="49">
         <v>3450056258</v>
       </c>
       <c r="F10" s="12" t="s">
@@ -3054,7 +3188,7 @@
       <c r="D11" s="25">
         <v>134069140</v>
       </c>
-      <c r="E11" s="50">
+      <c r="E11" s="49">
         <v>3450060988</v>
       </c>
       <c r="F11" s="12" t="s">
@@ -3083,7 +3217,7 @@
       <c r="D12" s="25">
         <v>134071914</v>
       </c>
-      <c r="E12" s="50">
+      <c r="E12" s="49">
         <v>3450061186</v>
       </c>
       <c r="F12" s="12" t="s">
@@ -3112,7 +3246,7 @@
       <c r="D13" s="25">
         <v>134032849</v>
       </c>
-      <c r="E13" s="50">
+      <c r="E13" s="49">
         <v>3450059349</v>
       </c>
       <c r="F13" s="12" t="s">
@@ -3141,7 +3275,7 @@
       <c r="D14" s="25">
         <v>134075165</v>
       </c>
-      <c r="E14" s="50">
+      <c r="E14" s="49">
         <v>3450061373</v>
       </c>
       <c r="F14" s="12" t="s">
@@ -3170,7 +3304,7 @@
       <c r="D15" s="25">
         <v>133991881</v>
       </c>
-      <c r="E15" s="50">
+      <c r="E15" s="49">
         <v>3450057215</v>
       </c>
       <c r="F15" s="12" t="s">
@@ -3199,7 +3333,7 @@
       <c r="D16" s="25">
         <v>134080037</v>
       </c>
-      <c r="E16" s="50">
+      <c r="E16" s="49">
         <v>3450061648</v>
       </c>
       <c r="F16" s="12" t="s">
@@ -3228,7 +3362,7 @@
       <c r="D17" s="25">
         <v>134082173</v>
       </c>
-      <c r="E17" s="50">
+      <c r="E17" s="49">
         <v>3450061802</v>
       </c>
       <c r="F17" s="12" t="s">
@@ -3257,7 +3391,7 @@
       <c r="D18" s="25">
         <v>134097930</v>
       </c>
-      <c r="E18" s="50">
+      <c r="E18" s="49">
         <v>3450058854</v>
       </c>
       <c r="F18" s="12" t="s">
@@ -3286,7 +3420,7 @@
       <c r="D19" s="25">
         <v>133980373</v>
       </c>
-      <c r="E19" s="50">
+      <c r="E19" s="49">
         <v>3450055378</v>
       </c>
       <c r="F19" s="12" t="s">
@@ -3315,7 +3449,7 @@
       <c r="D20" s="25">
         <v>134034881</v>
       </c>
-      <c r="E20" s="50">
+      <c r="E20" s="49">
         <v>3450059460</v>
       </c>
       <c r="F20" s="12" t="s">
@@ -3344,7 +3478,7 @@
       <c r="D21" s="25">
         <v>133997076</v>
       </c>
-      <c r="E21" s="50">
+      <c r="E21" s="49">
         <v>3450057303</v>
       </c>
       <c r="F21" s="12" t="s">
@@ -3373,7 +3507,7 @@
       <c r="D22" s="25">
         <v>133922899</v>
       </c>
-      <c r="E22" s="50">
+      <c r="E22" s="49">
         <v>3450053420</v>
       </c>
       <c r="F22" s="12" t="s">
@@ -3402,7 +3536,7 @@
       <c r="D23" s="25">
         <v>133982224</v>
       </c>
-      <c r="E23" s="50">
+      <c r="E23" s="49">
         <v>3450056588</v>
       </c>
       <c r="F23" s="12" t="s">
@@ -3431,7 +3565,7 @@
       <c r="D24" s="25">
         <v>133974816</v>
       </c>
-      <c r="E24" s="50">
+      <c r="E24" s="49">
         <v>3450056192</v>
       </c>
       <c r="F24" s="12" t="s">
@@ -3460,7 +3594,7 @@
       <c r="D25" s="25">
         <v>133978116</v>
       </c>
-      <c r="E25" s="50">
+      <c r="E25" s="49">
         <v>3450054135</v>
       </c>
       <c r="F25" s="12" t="s">
@@ -3489,7 +3623,7 @@
       <c r="D26" s="25">
         <v>133980382</v>
       </c>
-      <c r="E26" s="50">
+      <c r="E26" s="49">
         <v>3450056490</v>
       </c>
       <c r="F26" s="12" t="s">
@@ -3518,7 +3652,7 @@
       <c r="D27" s="25">
         <v>133981246</v>
       </c>
-      <c r="E27" s="50">
+      <c r="E27" s="49">
         <v>3450056577</v>
       </c>
       <c r="F27" s="12" t="s">
@@ -3547,7 +3681,7 @@
       <c r="D28" s="25">
         <v>133981548</v>
       </c>
-      <c r="E28" s="50">
+      <c r="E28" s="49">
         <v>3450054949</v>
       </c>
       <c r="F28" s="12" t="s">
@@ -3576,7 +3710,7 @@
       <c r="D29" s="25">
         <v>133982313</v>
       </c>
-      <c r="E29" s="50">
+      <c r="E29" s="49">
         <v>3450054806</v>
       </c>
       <c r="F29" s="12" t="s">
@@ -3605,7 +3739,7 @@
       <c r="D30" s="25">
         <v>133987942</v>
       </c>
-      <c r="E30" s="50">
+      <c r="E30" s="49">
         <v>3450056852</v>
       </c>
       <c r="F30" s="12" t="s">
@@ -3634,7 +3768,7 @@
       <c r="D31" s="25">
         <v>133988895</v>
       </c>
-      <c r="E31" s="50">
+      <c r="E31" s="49">
         <v>3450056973</v>
       </c>
       <c r="F31" s="12" t="s">
@@ -3663,7 +3797,7 @@
       <c r="D32" s="25">
         <v>133989544</v>
       </c>
-      <c r="E32" s="50">
+      <c r="E32" s="49">
         <v>3450057028</v>
       </c>
       <c r="F32" s="12" t="s">
@@ -3692,7 +3826,7 @@
       <c r="D33" s="25">
         <v>133990516</v>
       </c>
-      <c r="E33" s="50">
+      <c r="E33" s="49">
         <v>3450057094</v>
       </c>
       <c r="F33" s="12" t="s">
@@ -3721,7 +3855,7 @@
       <c r="D34" s="25">
         <v>133990572</v>
       </c>
-      <c r="E34" s="51">
+      <c r="E34" s="50">
         <v>3450057105</v>
       </c>
       <c r="F34" s="12" t="s">
@@ -4034,7 +4168,7 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="52" t="s">
         <v>120</v>
       </c>
       <c r="C2" s="28" t="s">
@@ -4043,7 +4177,7 @@
       <c r="D2" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="55">
+      <c r="E2" s="54">
         <v>3450061791</v>
       </c>
       <c r="F2" s="12" t="s">
@@ -4060,7 +4194,7 @@
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="52" t="s">
         <v>124</v>
       </c>
       <c r="C3" s="28" t="s">
@@ -4069,7 +4203,7 @@
       <c r="D3" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="55">
+      <c r="E3" s="54">
         <v>3450056181</v>
       </c>
       <c r="F3" s="12" t="s">
@@ -4086,7 +4220,7 @@
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="53" t="s">
+      <c r="B4" s="52" t="s">
         <v>124</v>
       </c>
       <c r="C4" s="28" t="s">
@@ -4095,7 +4229,7 @@
       <c r="D4" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="55">
+      <c r="E4" s="54">
         <v>3450058689</v>
       </c>
       <c r="F4" s="12" t="s">
@@ -4112,7 +4246,7 @@
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="53" t="s">
+      <c r="B5" s="52" t="s">
         <v>129</v>
       </c>
       <c r="C5" s="28" t="s">
@@ -4121,7 +4255,7 @@
       <c r="D5" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="55">
+      <c r="E5" s="54">
         <v>3450059866</v>
       </c>
       <c r="F5" s="12" t="s">
@@ -4138,7 +4272,7 @@
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="53" t="s">
+      <c r="B6" s="52" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="28" t="s">
@@ -4147,7 +4281,7 @@
       <c r="D6" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="55">
+      <c r="E6" s="54">
         <v>3450062682</v>
       </c>
       <c r="F6" s="12" t="s">
@@ -4164,7 +4298,7 @@
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="53" t="s">
+      <c r="B7" s="52" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="28" t="s">
@@ -4173,7 +4307,7 @@
       <c r="D7" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="55">
+      <c r="E7" s="54">
         <v>3450062385</v>
       </c>
       <c r="F7" s="12" t="s">
@@ -4190,16 +4324,16 @@
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="53" t="s">
+      <c r="B8" s="52" t="s">
         <v>134</v>
       </c>
       <c r="C8" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="D8" s="54" t="s">
+      <c r="D8" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="55">
+      <c r="E8" s="54">
         <v>3450064145</v>
       </c>
       <c r="F8" s="31" t="s">
@@ -4216,7 +4350,7 @@
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="53">
+      <c r="B9" s="52">
         <v>45883</v>
       </c>
       <c r="C9" s="28" t="s">
@@ -4245,7 +4379,7 @@
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="53">
+      <c r="B10" s="52">
         <v>45888</v>
       </c>
       <c r="C10" s="28" t="s">
@@ -4274,7 +4408,7 @@
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="53">
+      <c r="B11" s="52">
         <v>45888</v>
       </c>
       <c r="C11" s="28" t="s">
@@ -4303,7 +4437,7 @@
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="53">
+      <c r="B12" s="52">
         <v>45888</v>
       </c>
       <c r="C12" s="28" t="s">
@@ -4332,7 +4466,7 @@
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="53">
+      <c r="B13" s="52">
         <v>45888</v>
       </c>
       <c r="C13" s="28" t="s">
@@ -4361,7 +4495,7 @@
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="53">
+      <c r="B14" s="52">
         <v>45888</v>
       </c>
       <c r="C14" s="28" t="s">
@@ -4390,7 +4524,7 @@
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="53">
+      <c r="B15" s="52">
         <v>45889</v>
       </c>
       <c r="C15" s="28" t="s">
@@ -4419,7 +4553,7 @@
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="53">
+      <c r="B16" s="52">
         <v>45888</v>
       </c>
       <c r="C16" s="28" t="s">
@@ -4448,7 +4582,7 @@
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="53">
+      <c r="B17" s="52">
         <v>45888</v>
       </c>
       <c r="C17" s="28" t="s">
@@ -4477,7 +4611,7 @@
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="53">
+      <c r="B18" s="52">
         <v>45922</v>
       </c>
       <c r="C18" s="28" t="s">
@@ -4506,7 +4640,7 @@
       <c r="A19" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="53">
+      <c r="B19" s="52">
         <v>45894</v>
       </c>
       <c r="C19" s="28" t="s">
@@ -4535,7 +4669,7 @@
       <c r="A20" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="53">
+      <c r="B20" s="52">
         <v>45894</v>
       </c>
       <c r="C20" s="28" t="s">
@@ -4564,7 +4698,7 @@
       <c r="A21" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="53">
+      <c r="B21" s="52">
         <v>45914</v>
       </c>
       <c r="C21" s="28" t="s">
@@ -4593,7 +4727,7 @@
       <c r="A22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="53">
+      <c r="B22" s="52">
         <v>45895</v>
       </c>
       <c r="C22" s="28" t="s">
@@ -4622,7 +4756,7 @@
       <c r="A23" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B23" s="53">
+      <c r="B23" s="52">
         <v>45888</v>
       </c>
       <c r="C23" s="28" t="s">
@@ -4651,7 +4785,7 @@
       <c r="A24" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B24" s="53">
+      <c r="B24" s="52">
         <v>45898</v>
       </c>
       <c r="C24" s="28" t="s">
@@ -4680,7 +4814,7 @@
       <c r="A25" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B25" s="53">
+      <c r="B25" s="52">
         <v>45888</v>
       </c>
       <c r="C25" s="28" t="s">
@@ -4709,7 +4843,7 @@
       <c r="A26" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B26" s="53">
+      <c r="B26" s="52">
         <v>45888</v>
       </c>
       <c r="C26" s="28" t="s">
@@ -4738,7 +4872,7 @@
       <c r="A27" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B27" s="53">
+      <c r="B27" s="52">
         <v>45888</v>
       </c>
       <c r="C27" s="28" t="s">
@@ -4767,7 +4901,7 @@
       <c r="A28" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B28" s="53">
+      <c r="B28" s="52">
         <v>45888</v>
       </c>
       <c r="C28" s="28" t="s">
@@ -4796,7 +4930,7 @@
       <c r="A29" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B29" s="53">
+      <c r="B29" s="52">
         <v>45888</v>
       </c>
       <c r="C29" s="28" t="s">
@@ -4825,7 +4959,7 @@
       <c r="A30" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B30" s="53">
+      <c r="B30" s="52">
         <v>45888</v>
       </c>
       <c r="C30" s="28" t="s">
@@ -4854,7 +4988,7 @@
       <c r="A31" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="53">
+      <c r="B31" s="52">
         <v>45888</v>
       </c>
       <c r="C31" s="28" t="s">
@@ -4883,7 +5017,7 @@
       <c r="A32" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B32" s="53">
+      <c r="B32" s="52">
         <v>45888</v>
       </c>
       <c r="C32" s="28" t="s">
@@ -4912,7 +5046,7 @@
       <c r="A33" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B33" s="53">
+      <c r="B33" s="52">
         <v>45888</v>
       </c>
       <c r="C33" s="28" t="s">
@@ -4939,17 +5073,17 @@
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="6"/>
-      <c r="B34" s="53"/>
+      <c r="B34" s="52"/>
       <c r="C34" s="28"/>
-      <c r="D34" s="47"/>
-      <c r="E34" s="48"/>
+      <c r="D34" s="46"/>
+      <c r="E34" s="47"/>
       <c r="F34" s="36"/>
       <c r="G34" s="24"/>
       <c r="H34" s="9"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="6"/>
-      <c r="B35" s="53"/>
+      <c r="B35" s="52"/>
       <c r="C35" s="28"/>
       <c r="D35" s="25"/>
       <c r="E35" s="18"/>
@@ -5104,13 +5238,13 @@
       <c r="C2" s="28">
         <v>45897</v>
       </c>
-      <c r="D2" s="57">
+      <c r="D2" s="25">
         <v>134037866</v>
       </c>
       <c r="E2" s="18">
         <v>3450059690</v>
       </c>
-      <c r="F2" s="56" t="s">
+      <c r="F2" s="12" t="s">
         <v>166</v>
       </c>
       <c r="G2" s="24" t="s">
@@ -5133,19 +5267,19 @@
       <c r="C3" s="28">
         <v>45897</v>
       </c>
-      <c r="D3" s="57">
+      <c r="D3" s="25">
         <v>134030410</v>
       </c>
       <c r="E3" s="18">
         <v>3450059140</v>
       </c>
-      <c r="F3" s="58" t="s">
+      <c r="F3" s="19" t="s">
         <v>167</v>
       </c>
       <c r="G3" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="H3" s="59" t="s">
+      <c r="H3" s="9" t="s">
         <v>168</v>
       </c>
       <c r="I3" s="27">
@@ -5162,19 +5296,19 @@
       <c r="C4" s="28">
         <v>45897</v>
       </c>
-      <c r="D4" s="57">
+      <c r="D4" s="25">
         <v>134085449</v>
       </c>
       <c r="E4" s="18">
         <v>3450062100</v>
       </c>
-      <c r="F4" s="58" t="s">
+      <c r="F4" s="19" t="s">
         <v>169</v>
       </c>
       <c r="G4" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="59" t="s">
+      <c r="H4" s="9" t="s">
         <v>170</v>
       </c>
       <c r="I4" s="27">
@@ -5191,19 +5325,19 @@
       <c r="C5" s="28">
         <v>45897</v>
       </c>
-      <c r="D5" s="57">
+      <c r="D5" s="25">
         <v>134081882</v>
       </c>
       <c r="E5" s="18">
         <v>3450061769</v>
       </c>
-      <c r="F5" s="58" t="s">
+      <c r="F5" s="19" t="s">
         <v>171</v>
       </c>
       <c r="G5" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="59" t="s">
+      <c r="H5" s="9" t="s">
         <v>172</v>
       </c>
       <c r="I5" s="27">
@@ -5220,19 +5354,19 @@
       <c r="C6" s="28">
         <v>45897</v>
       </c>
-      <c r="D6" s="57">
+      <c r="D6" s="25">
         <v>134120327</v>
       </c>
       <c r="E6" s="18">
         <v>3450063848</v>
       </c>
-      <c r="F6" s="58" t="s">
+      <c r="F6" s="19" t="s">
         <v>173</v>
       </c>
       <c r="G6" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="H6" s="59" t="s">
+      <c r="H6" s="9" t="s">
         <v>168</v>
       </c>
       <c r="I6" s="27">
@@ -5249,19 +5383,19 @@
       <c r="C7" s="28">
         <v>45897</v>
       </c>
-      <c r="D7" s="57">
+      <c r="D7" s="25">
         <v>134123005</v>
       </c>
       <c r="E7" s="18">
         <v>3450064090</v>
       </c>
-      <c r="F7" s="58" t="s">
+      <c r="F7" s="19" t="s">
         <v>174</v>
       </c>
       <c r="G7" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="H7" s="59" t="s">
+      <c r="H7" s="9" t="s">
         <v>168</v>
       </c>
       <c r="I7" s="27">
@@ -5278,19 +5412,19 @@
       <c r="C8" s="28">
         <v>45897</v>
       </c>
-      <c r="D8" s="57">
+      <c r="D8" s="25">
         <v>134151226</v>
       </c>
       <c r="E8" s="18">
         <v>3450065828</v>
       </c>
-      <c r="F8" s="58" t="s">
+      <c r="F8" s="19" t="s">
         <v>175</v>
       </c>
       <c r="G8" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="H8" s="59" t="s">
+      <c r="H8" s="9" t="s">
         <v>35</v>
       </c>
       <c r="I8" s="27">
@@ -5307,19 +5441,19 @@
       <c r="C9" s="28">
         <v>45897</v>
       </c>
-      <c r="D9" s="57">
+      <c r="D9" s="25">
         <v>134156211</v>
       </c>
       <c r="E9" s="18">
         <v>3450062121</v>
       </c>
-      <c r="F9" s="58" t="s">
+      <c r="F9" s="19" t="s">
         <v>176</v>
       </c>
       <c r="G9" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="H9" s="59" t="s">
+      <c r="H9" s="9" t="s">
         <v>35</v>
       </c>
       <c r="I9" s="27">
@@ -5336,19 +5470,19 @@
       <c r="C10" s="28">
         <v>45897</v>
       </c>
-      <c r="D10" s="57">
+      <c r="D10" s="25">
         <v>133953737</v>
       </c>
       <c r="E10" s="18">
         <v>3450054916</v>
       </c>
-      <c r="F10" s="58" t="s">
+      <c r="F10" s="19" t="s">
         <v>177</v>
       </c>
       <c r="G10" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="H10" s="59" t="s">
+      <c r="H10" s="9" t="s">
         <v>178</v>
       </c>
       <c r="I10" s="27">
@@ -5365,19 +5499,19 @@
       <c r="C11" s="28">
         <v>45897</v>
       </c>
-      <c r="D11" s="57">
+      <c r="D11" s="25">
         <v>133956942</v>
       </c>
       <c r="E11" s="18">
         <v>3450055213</v>
       </c>
-      <c r="F11" s="58" t="s">
+      <c r="F11" s="19" t="s">
         <v>179</v>
       </c>
       <c r="G11" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="H11" s="59" t="s">
+      <c r="H11" s="9" t="s">
         <v>106</v>
       </c>
       <c r="I11" s="27">
@@ -5394,19 +5528,19 @@
       <c r="C12" s="28">
         <v>45897</v>
       </c>
-      <c r="D12" s="57">
+      <c r="D12" s="25">
         <v>133957208</v>
       </c>
       <c r="E12" s="18">
         <v>3450055268</v>
       </c>
-      <c r="F12" s="58" t="s">
+      <c r="F12" s="19" t="s">
         <v>171</v>
       </c>
       <c r="G12" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="H12" s="59" t="s">
+      <c r="H12" s="9" t="s">
         <v>180</v>
       </c>
       <c r="I12" s="27">
@@ -5423,19 +5557,19 @@
       <c r="C13" s="28">
         <v>45897</v>
       </c>
-      <c r="D13" s="57">
+      <c r="D13" s="25">
         <v>133969078</v>
       </c>
       <c r="E13" s="18">
         <v>3450056060</v>
       </c>
-      <c r="F13" s="58" t="s">
+      <c r="F13" s="19" t="s">
         <v>181</v>
       </c>
       <c r="G13" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="H13" s="59" t="s">
+      <c r="H13" s="9" t="s">
         <v>182</v>
       </c>
       <c r="I13" s="27">
@@ -5452,19 +5586,19 @@
       <c r="C14" s="28">
         <v>45897</v>
       </c>
-      <c r="D14" s="57">
+      <c r="D14" s="25">
         <v>133968156</v>
       </c>
       <c r="E14" s="18">
         <v>3450056049</v>
       </c>
-      <c r="F14" s="58" t="s">
+      <c r="F14" s="19" t="s">
         <v>183</v>
       </c>
       <c r="G14" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="H14" s="59" t="s">
+      <c r="H14" s="9" t="s">
         <v>168</v>
       </c>
       <c r="I14" s="27">
@@ -5481,19 +5615,19 @@
       <c r="C15" s="28">
         <v>45897</v>
       </c>
-      <c r="D15" s="57">
+      <c r="D15" s="25">
         <v>134028341</v>
       </c>
       <c r="E15" s="18">
         <v>3450059030</v>
       </c>
-      <c r="F15" s="58" t="s">
+      <c r="F15" s="19" t="s">
         <v>184</v>
       </c>
       <c r="G15" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="59" t="s">
+      <c r="H15" s="9" t="s">
         <v>185</v>
       </c>
       <c r="I15" s="27">
@@ -5510,19 +5644,19 @@
       <c r="C16" s="28">
         <v>45897</v>
       </c>
-      <c r="D16" s="57">
+      <c r="D16" s="25">
         <v>133980074</v>
       </c>
       <c r="E16" s="18">
         <v>3450056478</v>
       </c>
-      <c r="F16" s="58" t="s">
+      <c r="F16" s="19" t="s">
         <v>186</v>
       </c>
       <c r="G16" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="59" t="s">
+      <c r="H16" s="9" t="s">
         <v>187</v>
       </c>
       <c r="I16" s="27">
@@ -5539,19 +5673,19 @@
       <c r="C17" s="28">
         <v>45897</v>
       </c>
-      <c r="D17" s="57">
+      <c r="D17" s="25">
         <v>134046643</v>
       </c>
       <c r="E17" s="18">
         <v>3450059987</v>
       </c>
-      <c r="F17" s="58" t="s">
+      <c r="F17" s="19" t="s">
         <v>188</v>
       </c>
       <c r="G17" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="H17" s="59" t="s">
+      <c r="H17" s="9" t="s">
         <v>35</v>
       </c>
       <c r="I17" s="27">
@@ -5568,19 +5702,19 @@
       <c r="C18" s="28">
         <v>45897</v>
       </c>
-      <c r="D18" s="57">
+      <c r="D18" s="25">
         <v>134021045</v>
       </c>
       <c r="E18" s="18">
         <v>3450058744</v>
       </c>
-      <c r="F18" s="58" t="s">
+      <c r="F18" s="19" t="s">
         <v>189</v>
       </c>
       <c r="G18" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H18" s="59" t="s">
+      <c r="H18" s="9" t="s">
         <v>190</v>
       </c>
       <c r="I18" s="27">
@@ -5597,19 +5731,19 @@
       <c r="C19" s="28">
         <v>45897</v>
       </c>
-      <c r="D19" s="57">
+      <c r="D19" s="25">
         <v>134028122</v>
       </c>
       <c r="E19" s="18">
         <v>3450059019</v>
       </c>
-      <c r="F19" s="58" t="s">
+      <c r="F19" s="19" t="s">
         <v>184</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H19" s="59" t="s">
+      <c r="H19" s="9" t="s">
         <v>191</v>
       </c>
       <c r="I19" s="27">
@@ -5626,19 +5760,19 @@
       <c r="C20" s="28">
         <v>45897</v>
       </c>
-      <c r="D20" s="57">
+      <c r="D20" s="25">
         <v>133961625</v>
       </c>
       <c r="E20" s="18">
         <v>3450055521</v>
       </c>
-      <c r="F20" s="58" t="s">
+      <c r="F20" s="19" t="s">
         <v>192</v>
       </c>
       <c r="G20" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="H20" s="59" t="s">
+      <c r="H20" s="9" t="s">
         <v>193</v>
       </c>
       <c r="I20" s="27">
@@ -5655,13 +5789,13 @@
       <c r="C21" s="28">
         <v>45897</v>
       </c>
-      <c r="D21" s="57">
+      <c r="D21" s="25">
         <v>134026947</v>
       </c>
       <c r="E21" s="18">
         <v>3450058920</v>
       </c>
-      <c r="F21" s="56" t="s">
+      <c r="F21" s="12" t="s">
         <v>194</v>
       </c>
       <c r="G21" s="20" t="s">
@@ -5684,13 +5818,13 @@
       <c r="C22" s="28">
         <v>45897</v>
       </c>
-      <c r="D22" s="57">
+      <c r="D22" s="25">
         <v>134027915</v>
       </c>
       <c r="E22" s="18">
         <v>3450058975</v>
       </c>
-      <c r="F22" s="58" t="s">
+      <c r="F22" s="19" t="s">
         <v>195</v>
       </c>
       <c r="G22" s="20" t="s">
@@ -5713,13 +5847,13 @@
       <c r="C23" s="28">
         <v>45897</v>
       </c>
-      <c r="D23" s="57">
+      <c r="D23" s="25">
         <v>134027953</v>
       </c>
       <c r="E23" s="18">
         <v>3450058975</v>
       </c>
-      <c r="F23" s="58" t="s">
+      <c r="F23" s="19" t="s">
         <v>196</v>
       </c>
       <c r="G23" s="20" t="s">
@@ -5742,13 +5876,13 @@
       <c r="C24" s="28">
         <v>45897</v>
       </c>
-      <c r="D24" s="57">
+      <c r="D24" s="25">
         <v>134029327</v>
       </c>
       <c r="E24" s="18">
         <v>3450059107</v>
       </c>
-      <c r="F24" s="58" t="s">
+      <c r="F24" s="19" t="s">
         <v>197</v>
       </c>
       <c r="G24" s="20" t="s">
@@ -5771,13 +5905,13 @@
       <c r="C25" s="28">
         <v>45897</v>
       </c>
-      <c r="D25" s="57">
+      <c r="D25" s="25">
         <v>134033569</v>
       </c>
       <c r="E25" s="18">
         <v>3450059393</v>
       </c>
-      <c r="F25" s="56" t="s">
+      <c r="F25" s="12" t="s">
         <v>198</v>
       </c>
       <c r="G25" s="20" t="s">
@@ -5800,13 +5934,13 @@
       <c r="C26" s="28">
         <v>45897</v>
       </c>
-      <c r="D26" s="57">
+      <c r="D26" s="25">
         <v>134033796</v>
       </c>
       <c r="E26" s="18">
         <v>3450059404</v>
       </c>
-      <c r="F26" s="58" t="s">
+      <c r="F26" s="19" t="s">
         <v>199</v>
       </c>
       <c r="G26" s="20" t="s">
@@ -5829,13 +5963,13 @@
       <c r="C27" s="28">
         <v>45897</v>
       </c>
-      <c r="D27" s="57">
+      <c r="D27" s="25">
         <v>134037774</v>
       </c>
       <c r="E27" s="18">
         <v>3450059679</v>
       </c>
-      <c r="F27" s="58" t="s">
+      <c r="F27" s="19" t="s">
         <v>200</v>
       </c>
       <c r="G27" s="20" t="s">
@@ -5858,19 +5992,19 @@
       <c r="C28" s="28">
         <v>45897</v>
       </c>
-      <c r="D28" s="57">
+      <c r="D28" s="25">
         <v>134075647</v>
       </c>
       <c r="E28" s="18">
         <v>3450061406</v>
       </c>
-      <c r="F28" s="58" t="s">
+      <c r="F28" s="19" t="s">
         <v>201</v>
       </c>
       <c r="G28" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="H28" s="59" t="s">
+      <c r="H28" s="9" t="s">
         <v>202</v>
       </c>
       <c r="I28" s="27">
@@ -6127,14 +6261,14 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43D38813-FAE5-45C6-9D51-7607EDAA916D}">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" customWidth="1"/>
     <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.5703125" style="17" customWidth="1"/>
-    <col min="5" max="5" width="21.5703125" customWidth="1"/>
+    <col min="5" max="5" width="21.5703125" style="17" customWidth="1"/>
     <col min="6" max="6" width="36.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.85546875" customWidth="1"/>
     <col min="8" max="8" width="20.85546875" customWidth="1"/>
@@ -6163,7 +6297,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="44" t="s">
+      <c r="H1" s="43" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -6174,240 +6308,530 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="27"/>
+      <c r="B2" s="7">
+        <v>45884</v>
+      </c>
+      <c r="C2" s="28">
+        <v>45898</v>
+      </c>
+      <c r="D2" s="56">
+        <v>134048500</v>
+      </c>
+      <c r="E2" s="18">
+        <v>3450055389</v>
+      </c>
+      <c r="F2" s="55" t="s">
+        <v>203</v>
+      </c>
+      <c r="G2" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" s="59" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" s="27">
+        <v>45884</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="27"/>
+      <c r="B3" s="7">
+        <v>45887</v>
+      </c>
+      <c r="C3" s="28">
+        <v>45898</v>
+      </c>
+      <c r="D3" s="56">
+        <v>133979133</v>
+      </c>
+      <c r="E3" s="18">
+        <v>3450056379</v>
+      </c>
+      <c r="F3" s="55" t="s">
+        <v>204</v>
+      </c>
+      <c r="G3" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="I3" s="27">
+        <v>45894</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="27"/>
+      <c r="B4" s="7">
+        <v>45887</v>
+      </c>
+      <c r="C4" s="28">
+        <v>45898</v>
+      </c>
+      <c r="D4" s="56">
+        <v>134050897</v>
+      </c>
+      <c r="E4" s="18">
+        <v>3450056357</v>
+      </c>
+      <c r="F4" s="55" t="s">
+        <v>205</v>
+      </c>
+      <c r="G4" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="59" t="s">
+        <v>89</v>
+      </c>
+      <c r="I4" s="27">
+        <v>45887</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="27"/>
+      <c r="B5" s="7">
+        <v>45888</v>
+      </c>
+      <c r="C5" s="28">
+        <v>45898</v>
+      </c>
+      <c r="D5" s="56">
+        <v>134058118</v>
+      </c>
+      <c r="E5" s="18">
+        <v>3450060581</v>
+      </c>
+      <c r="F5" s="55" t="s">
+        <v>206</v>
+      </c>
+      <c r="G5" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="I5" s="27">
+        <v>45888</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="27"/>
+      <c r="B6" s="7">
+        <v>45890</v>
+      </c>
+      <c r="C6" s="28">
+        <v>45898</v>
+      </c>
+      <c r="D6" s="56">
+        <v>134057758</v>
+      </c>
+      <c r="E6" s="18">
+        <v>3450060548</v>
+      </c>
+      <c r="F6" s="55" t="s">
+        <v>207</v>
+      </c>
+      <c r="G6" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="60" t="s">
+        <v>208</v>
+      </c>
+      <c r="I6" s="27">
+        <v>45897</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="27"/>
+      <c r="B7" s="7">
+        <v>45887</v>
+      </c>
+      <c r="C7" s="28">
+        <v>45898</v>
+      </c>
+      <c r="D7" s="56">
+        <v>134049809</v>
+      </c>
+      <c r="E7" s="18">
+        <v>3450056764</v>
+      </c>
+      <c r="F7" s="55" t="s">
+        <v>209</v>
+      </c>
+      <c r="G7" s="44" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="40" t="s">
+        <v>84</v>
+      </c>
+      <c r="I7" s="27">
+        <v>45887</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="27"/>
+      <c r="B8" s="7">
+        <v>45896</v>
+      </c>
+      <c r="C8" s="28">
+        <v>45898</v>
+      </c>
+      <c r="D8" s="56">
+        <v>134140085</v>
+      </c>
+      <c r="E8" s="18">
+        <v>3450065135</v>
+      </c>
+      <c r="F8" s="55" t="s">
+        <v>207</v>
+      </c>
+      <c r="G8" s="45" t="s">
+        <v>137</v>
+      </c>
+      <c r="H8" s="60" t="s">
+        <v>210</v>
+      </c>
+      <c r="I8" s="27">
+        <v>45896</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="46"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="27"/>
+      <c r="B9" s="7">
+        <v>45896</v>
+      </c>
+      <c r="C9" s="28">
+        <v>45898</v>
+      </c>
+      <c r="D9" s="56">
+        <v>134157687</v>
+      </c>
+      <c r="E9" s="18">
+        <v>3450066235</v>
+      </c>
+      <c r="F9" s="55" t="s">
+        <v>211</v>
+      </c>
+      <c r="G9" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="59" t="s">
+        <v>212</v>
+      </c>
+      <c r="I9" s="27">
+        <v>45898</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="27"/>
+      <c r="B10" s="7">
+        <v>45896</v>
+      </c>
+      <c r="C10" s="28">
+        <v>45898</v>
+      </c>
+      <c r="D10" s="56">
+        <v>134150333</v>
+      </c>
+      <c r="E10" s="18">
+        <v>3450065740</v>
+      </c>
+      <c r="F10" s="55" t="s">
+        <v>213</v>
+      </c>
+      <c r="G10" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="I10" s="27">
+        <v>45898</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="27"/>
+      <c r="B11" s="7">
+        <v>45896</v>
+      </c>
+      <c r="C11" s="28">
+        <v>45898</v>
+      </c>
+      <c r="D11" s="56">
+        <v>134147149</v>
+      </c>
+      <c r="E11" s="18">
+        <v>3450065520</v>
+      </c>
+      <c r="F11" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="G11" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="H11" s="59" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" s="27">
+        <v>45896</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="27"/>
+      <c r="B12" s="7">
+        <v>45887</v>
+      </c>
+      <c r="C12" s="28">
+        <v>45898</v>
+      </c>
+      <c r="D12" s="56">
+        <v>133976007</v>
+      </c>
+      <c r="E12" s="18">
+        <v>3450056225</v>
+      </c>
+      <c r="F12" s="55" t="s">
+        <v>215</v>
+      </c>
+      <c r="G12" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" s="59" t="s">
+        <v>216</v>
+      </c>
+      <c r="I12" s="27">
+        <v>45891</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="27"/>
+      <c r="B13" s="7">
+        <v>45891</v>
+      </c>
+      <c r="C13" s="28">
+        <v>45898</v>
+      </c>
+      <c r="D13" s="56">
+        <v>133955750</v>
+      </c>
+      <c r="E13" s="18">
+        <v>3450055059</v>
+      </c>
+      <c r="F13" s="55" t="s">
+        <v>217</v>
+      </c>
+      <c r="G13" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="59" t="s">
+        <v>218</v>
+      </c>
+      <c r="I13" s="27">
+        <v>45889</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="27"/>
+      <c r="B14" s="7">
+        <v>45891</v>
+      </c>
+      <c r="C14" s="28">
+        <v>45898</v>
+      </c>
+      <c r="D14" s="56">
+        <v>133990957</v>
+      </c>
+      <c r="E14" s="18">
+        <v>3450057138</v>
+      </c>
+      <c r="F14" s="55" t="s">
+        <v>219</v>
+      </c>
+      <c r="G14" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="59" t="s">
+        <v>220</v>
+      </c>
+      <c r="I14" s="27">
+        <v>45896</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="27"/>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="27"/>
-    </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1">
-      <c r="A17" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="27"/>
+      <c r="B15" s="7">
+        <v>45891</v>
+      </c>
+      <c r="C15" s="28">
+        <v>45898</v>
+      </c>
+      <c r="D15" s="56">
+        <v>134073293</v>
+      </c>
+      <c r="E15" s="18">
+        <v>3450061307</v>
+      </c>
+      <c r="F15" s="55" t="s">
+        <v>221</v>
+      </c>
+      <c r="G15" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="H15" s="59" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15" s="27">
+        <v>45891</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15" customHeight="1">
+      <c r="A16" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="7">
+        <v>45890</v>
+      </c>
+      <c r="C16" s="28">
+        <v>45898</v>
+      </c>
+      <c r="D16" s="56">
+        <v>134048206</v>
+      </c>
+      <c r="E16" s="18">
+        <v>3450060042</v>
+      </c>
+      <c r="F16" s="55" t="s">
+        <v>222</v>
+      </c>
+      <c r="G16" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="38" t="s">
+        <v>84</v>
+      </c>
+      <c r="I16" s="27">
+        <v>45890</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="7">
+        <v>45884</v>
+      </c>
+      <c r="C17" s="28">
+        <v>45898</v>
+      </c>
+      <c r="D17" s="56">
+        <v>134048620</v>
+      </c>
+      <c r="E17" s="18">
+        <v>3450055224</v>
+      </c>
+      <c r="F17" s="55" t="s">
+        <v>223</v>
+      </c>
+      <c r="G17" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="59" t="s">
+        <v>224</v>
+      </c>
+      <c r="I17" s="27">
+        <v>45896</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="46"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="27"/>
+      <c r="B18" s="7">
+        <v>45890</v>
+      </c>
+      <c r="C18" s="28">
+        <v>45898</v>
+      </c>
+      <c r="D18" s="56">
+        <v>134050664</v>
+      </c>
+      <c r="E18" s="18">
+        <v>3450060152</v>
+      </c>
+      <c r="F18" s="55" t="s">
+        <v>225</v>
+      </c>
+      <c r="G18" s="57" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I18" s="27">
+        <v>45890</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="27"/>
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>45890</v>
+      </c>
+      <c r="C19" s="28">
+        <v>45898</v>
+      </c>
+      <c r="D19" s="56">
+        <v>134053988</v>
+      </c>
+      <c r="E19" s="18">
+        <v>3450060284</v>
+      </c>
+      <c r="F19" s="55" t="s">
+        <v>226</v>
+      </c>
+      <c r="G19" s="57" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I19" s="27">
+        <v>45890</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
       <c r="B20" s="8"/>
       <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
       <c r="F20" s="15"/>
       <c r="G20" s="34"/>
       <c r="H20" s="9"/>
@@ -6453,7 +6877,7 @@
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
-      <c r="G24" s="34"/>
+      <c r="G24" s="6"/>
       <c r="H24" s="9"/>
       <c r="I24" s="27"/>
     </row>
@@ -6576,7 +7000,7 @@
       <c r="F35" s="9"/>
       <c r="G35" s="6"/>
       <c r="H35" s="9"/>
-      <c r="I35" s="27"/>
+      <c r="I35"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
@@ -6787,28 +7211,17 @@
       <c r="H54" s="9"/>
       <c r="I54"/>
     </row>
-    <row r="55" spans="1:9">
-      <c r="A55" s="6"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="9"/>
-      <c r="I55"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="3">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{33F609D2-9B9D-4D52-B406-6DFCF1363D87}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A19" xr:uid="{33F609D2-9B9D-4D52-B406-6DFCF1363D87}">
       <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{1B2A036A-428B-43C6-B539-9B85A74E7043}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G40" xr:uid="{1B2A036A-428B-43C6-B539-9B85A74E7043}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6818,7 +7231,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B760CA2F-2CA8-44F2-8B49-339714F538DA}">
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="14.5703125" customWidth="1"/>
@@ -6864,94 +7277,212 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="27"/>
+      <c r="B2" s="7">
+        <v>45888</v>
+      </c>
+      <c r="C2" s="28">
+        <v>45899</v>
+      </c>
+      <c r="D2" s="56">
+        <v>134009983</v>
+      </c>
+      <c r="E2" s="18">
+        <v>3450058161</v>
+      </c>
+      <c r="F2" s="55" t="s">
+        <v>227</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="H2" s="58" t="s">
+        <v>228</v>
+      </c>
+      <c r="I2" s="37">
+        <v>45888</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="38"/>
+      <c r="B3" s="7">
+        <v>45891</v>
+      </c>
+      <c r="C3" s="28">
+        <v>45899</v>
+      </c>
+      <c r="D3" s="56">
+        <v>134078495</v>
+      </c>
+      <c r="E3" s="18">
+        <v>3450061538</v>
+      </c>
+      <c r="F3" s="55" t="s">
+        <v>229</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="58" t="s">
+        <v>230</v>
+      </c>
+      <c r="I3" s="27">
+        <v>45891</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="27"/>
+      <c r="B4" s="7">
+        <v>45891</v>
+      </c>
+      <c r="C4" s="28">
+        <v>45899</v>
+      </c>
+      <c r="D4" s="56">
+        <v>134078694</v>
+      </c>
+      <c r="E4" s="18">
+        <v>3450061549</v>
+      </c>
+      <c r="F4" s="55" t="s">
+        <v>231</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="58" t="s">
+        <v>232</v>
+      </c>
+      <c r="I4" s="27">
+        <v>45891</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="27"/>
+      <c r="B5" s="7">
+        <v>45898</v>
+      </c>
+      <c r="C5" s="28">
+        <v>45899</v>
+      </c>
+      <c r="D5" s="56">
+        <v>134195138</v>
+      </c>
+      <c r="E5" s="18">
+        <v>3450068040</v>
+      </c>
+      <c r="F5" s="55" t="s">
+        <v>233</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="58" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="27">
+        <v>45898</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="6"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="27"/>
+      <c r="A6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="7">
+        <v>45887</v>
+      </c>
+      <c r="C6" s="28">
+        <v>45899</v>
+      </c>
+      <c r="D6" s="56">
+        <v>133981227</v>
+      </c>
+      <c r="E6" s="18">
+        <v>3450056566</v>
+      </c>
+      <c r="F6" s="55" t="s">
+        <v>234</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="58" t="s">
+        <v>235</v>
+      </c>
+      <c r="I6" s="27">
+        <v>45894</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="6"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="11"/>
+      <c r="A7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="7">
+        <v>45891</v>
+      </c>
+      <c r="C7" s="28">
+        <v>45899</v>
+      </c>
+      <c r="D7" s="56">
+        <v>134080559</v>
+      </c>
+      <c r="E7" s="18">
+        <v>3450061670</v>
+      </c>
+      <c r="F7" s="55" t="s">
+        <v>236</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="I7" s="27">
+        <v>45897</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="6"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="11"/>
+      <c r="A8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="7">
+        <v>45891</v>
+      </c>
+      <c r="C8" s="28">
+        <v>45899</v>
+      </c>
+      <c r="D8" s="56">
+        <v>134067107</v>
+      </c>
+      <c r="E8" s="18">
+        <v>3450060878</v>
+      </c>
+      <c r="F8" s="55" t="s">
+        <v>237</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="58" t="s">
+        <v>238</v>
+      </c>
+      <c r="I8" s="27">
+        <v>45891</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="12"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="36"/>
       <c r="G9" s="6"/>
       <c r="H9" s="9"/>
       <c r="I9" s="11"/>
@@ -7002,33 +7533,31 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6"/>
-      <c r="B14" s="7"/>
+      <c r="B14" s="8"/>
       <c r="C14" s="7"/>
       <c r="D14" s="8"/>
       <c r="E14" s="14"/>
-      <c r="F14" s="12"/>
+      <c r="F14" s="13"/>
       <c r="G14" s="6"/>
       <c r="H14" s="9"/>
-      <c r="I14" s="11"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6"/>
-      <c r="B15" s="7"/>
+      <c r="B15" s="8"/>
       <c r="C15" s="7"/>
       <c r="D15" s="8"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="12"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="15"/>
       <c r="G15" s="6"/>
       <c r="H15" s="9"/>
-      <c r="I15" s="11"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6"/>
       <c r="B16" s="8"/>
       <c r="C16" s="7"/>
       <c r="D16" s="8"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="13"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="9"/>
       <c r="G16" s="6"/>
       <c r="H16" s="9"/>
     </row>
@@ -7038,7 +7567,7 @@
       <c r="C17" s="7"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="15"/>
+      <c r="F17" s="9"/>
       <c r="G17" s="6"/>
       <c r="H17" s="9"/>
     </row>
@@ -7372,38 +7901,21 @@
       <c r="G50" s="6"/>
       <c r="H50" s="9"/>
     </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="6"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="9"/>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="6"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="9"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="3">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F8 D2:D8">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G38" xr:uid="{F491B589-3891-4413-A332-CE5A1AB48EB2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G36" xr:uid="{F491B589-3891-4413-A332-CE5A1AB48EB2}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A15" xr:uid="{D22D2853-2B53-4F60-8CBE-3EBA3A5BA43C}">
-      <formula1>$J$2</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A13" xr:uid="{D22D2853-2B53-4F60-8CBE-3EBA3A5BA43C}">
+      <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8075,6 +8587,108 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-494894</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-494894</Url>
+      <Description>QAFFA7D2F2TC-2102087286-494894</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="43" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="abf1b9912853fe4a934dbc2373304754">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d8d96f03b10d24171ef462918d18284e" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -8446,120 +9060,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-494894</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-494894</Url>
-      <Description>QAFFA7D2F2TC-2102087286-494894</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F38E076B-DE6E-4067-90F8-8ED2CC8B8C04}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F38E076B-DE6E-4067-90F8-8ED2CC8B8C04}"/>
 </file>